--- a/inst/templates/DataImportConfiguration.xlsx
+++ b/inst/templates/DataImportConfiguration.xlsx
@@ -4,20 +4,26 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" firstSheet="0" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="DataFiles" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="tpDictionary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="pkDictionary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="NumericValues" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="_Validity" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="validity_DataFiles_DataClass_5">'_Validity'!$A$2:$A$6</definedName>
+    <definedName name="validity_tpDictionary_Type_7">'_Validity'!$A$8:$A$12</definedName>
+    <definedName name="validity_pkDictionary_Type_14">'_Validity'!$A$14:$A$18</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
   <si>
     <t xml:space="preserve">FileIdentifier</t>
   </si>
@@ -37,30 +43,7 @@
     <t xml:space="preserve">identifier for file filtering</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">path of csv file relative to configuration xlsx
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <i val="true"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">check also vignette data_import_by_dictionary</t>
-    </r>
+    <t xml:space="preserve">path of csv file relative to configuration xlsx. See vignette 'data_import_by_dictionary'</t>
   </si>
   <si>
     <t xml:space="preserve">sheet name for data dictionary</t>
@@ -108,42 +91,22 @@
     <t xml:space="preserve">Description</t>
   </si>
   <si>
-    <t xml:space="preserve">internal colum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name of column in source csv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">an R executable expression which is executed on source rows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">an R executable expression to set  Value for the filtered rows</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">check also vignette data_import_by_dictionary
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <i val="true"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Use double quotes " and not single quotes ' for strings</t>
-    </r>
+    <t xml:space="preserve">internal column name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source column name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">filter expression for rows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value assignment expression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See vignette 'data_import_by_dictionary'. Use double quotes for strings, not single quotes.</t>
   </si>
   <si>
     <t xml:space="preserve">studyId</t>
@@ -272,9 +235,6 @@
     <t xml:space="preserve">yMin</t>
   </si>
   <si>
-    <t xml:space="preserve">NA</t>
-  </si>
-  <si>
     <t xml:space="preserve">ignored for individual data or if yErrorType is geometric or arthmetric</t>
   </si>
   <si>
@@ -389,6 +349,15 @@
     <t xml:space="preserve">compartment</t>
   </si>
   <si>
+    <t xml:space="preserve">value assignment expression. Use double quotes for strings, not single quotes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See vignette 'data_import_by_dictionary'. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">paste(STUD,GRPNAME,"aggregated",sep="_")</t>
+  </si>
+  <si>
     <t xml:space="preserve">pkParameter</t>
   </si>
   <si>
@@ -440,16 +409,22 @@
     <t xml:space="preserve">Reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Numeric scalar value name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit of value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Additional context</t>
+    <t xml:space="preserve">Comment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">variable name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">numeric value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reference source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">user comments</t>
   </si>
   <si>
     <t xml:space="preserve">Dose</t>
@@ -461,7 +436,7 @@
     <t xml:space="preserve">mg</t>
   </si>
   <si>
-    <t xml:space="preserve">Study 1234</t>
+    <t xml:space="preserve">Study Report</t>
   </si>
   <si>
     <t xml:space="preserve">Single dose amount</t>
@@ -473,10 +448,25 @@
     <t xml:space="preserve">1.5</t>
   </si>
   <si>
-    <t xml:space="preserve">Protocol</t>
-  </si>
-  <si>
     <t xml:space="preserve">Infusion duration used in protocol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated list values for Excel data validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tpIndividual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tpAggregated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pkIndividual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pkAggregated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">numericValues</t>
   </si>
 </sst>
 </file>
@@ -486,7 +476,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -498,32 +488,23 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <b/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <i/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -552,38 +533,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="center" vertical="bottom" indent="0"/>
+      <protection hidden="0" locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="center" vertical="top" indent="0" wrapText="1"/>
+      <protection hidden="0" locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0"/>
       <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment textRotation="0" horizontal="center" vertical="bottom" indent="0"/>
       <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment textRotation="0" horizontal="center" vertical="top" indent="0" wrapText="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="center" vertical="bottom" indent="0" wrapText="1"/>
+      <protection hidden="0" locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0" wrapText="1"/>
       <protection hidden="0" locked="0"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0"/>
-      <protection hidden="0" locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0"/>
-      <protection hidden="0" locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment textRotation="0" horizontal="center" vertical="bottom" indent="0"/>
-      <protection hidden="0" locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment textRotation="0" horizontal="center" vertical="bottom" indent="0" wrapText="1"/>
-      <protection hidden="0" locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0" wrapText="1"/>
       <protection hidden="0" locked="0"/>
     </xf>
   </cellXfs>
@@ -843,3070 +820,3146 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="35.05" customHeight="1">
-      <c r="A2" s="3" t="s">
+    <row r="2" ht="34.5" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="3"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="E4" s="1"/>
+      <c r="E4" s="3"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="E5" s="1"/>
+      <c r="E5" s="3"/>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="E6" s="1"/>
+      <c r="E6" s="3"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="E7" s="1"/>
+      <c r="E7" s="3"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="E8" s="1"/>
+      <c r="E8" s="3"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="E9" s="1"/>
+      <c r="E9" s="3"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="E10" s="1"/>
+      <c r="E10" s="3"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="E11" s="1"/>
+      <c r="E11" s="3"/>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="E12" s="1"/>
+      <c r="E12" s="3"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="E13" s="1"/>
+      <c r="E13" s="3"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="E14" s="1"/>
+      <c r="E14" s="3"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="E15" s="1"/>
+      <c r="E15" s="3"/>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="E16" s="1"/>
+      <c r="E16" s="3"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="E17" s="1"/>
+      <c r="E17" s="3"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="E18" s="1"/>
+      <c r="E18" s="3"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="E19" s="1"/>
+      <c r="E19" s="3"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="E20" s="1"/>
+      <c r="E20" s="3"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="E21" s="1"/>
+      <c r="E21" s="3"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="E22" s="1"/>
+      <c r="E22" s="3"/>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="E23" s="1"/>
+      <c r="E23" s="3"/>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="E24" s="1"/>
+      <c r="E24" s="3"/>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="E25" s="1"/>
+      <c r="E25" s="3"/>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="E26" s="1"/>
+      <c r="E26" s="3"/>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="E27" s="1"/>
+      <c r="E27" s="3"/>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="E28" s="1"/>
+      <c r="E28" s="3"/>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="E29" s="1"/>
+      <c r="E29" s="3"/>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="E30" s="1"/>
+      <c r="E30" s="3"/>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="E31" s="1"/>
+      <c r="E31" s="3"/>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="E32" s="1"/>
+      <c r="E32" s="3"/>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="E33" s="1"/>
+      <c r="E33" s="3"/>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="E34" s="1"/>
+      <c r="E34" s="3"/>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="E35" s="1"/>
+      <c r="E35" s="3"/>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="E36" s="1"/>
+      <c r="E36" s="3"/>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="E37" s="1"/>
+      <c r="E37" s="3"/>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="E38" s="1"/>
+      <c r="E38" s="3"/>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="E39" s="1"/>
+      <c r="E39" s="3"/>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="E40" s="1"/>
+      <c r="E40" s="3"/>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="E41" s="1"/>
+      <c r="E41" s="3"/>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="E42" s="1"/>
+      <c r="E42" s="3"/>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="E43" s="1"/>
+      <c r="E43" s="3"/>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="E44" s="1"/>
+      <c r="E44" s="3"/>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c r="E45" s="1"/>
+      <c r="E45" s="3"/>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="E46" s="1"/>
+      <c r="E46" s="3"/>
     </row>
     <row r="47" ht="15" customHeight="1">
-      <c r="E47" s="1"/>
+      <c r="E47" s="3"/>
     </row>
     <row r="48" ht="15" customHeight="1">
-      <c r="E48" s="1"/>
+      <c r="E48" s="3"/>
     </row>
     <row r="49" ht="15" customHeight="1">
-      <c r="E49" s="1"/>
+      <c r="E49" s="3"/>
     </row>
     <row r="50" ht="15" customHeight="1">
-      <c r="E50" s="1"/>
+      <c r="E50" s="3"/>
     </row>
     <row r="51" ht="15" customHeight="1">
-      <c r="E51" s="1"/>
+      <c r="E51" s="3"/>
     </row>
     <row r="52" ht="15" customHeight="1">
-      <c r="E52" s="1"/>
+      <c r="E52" s="3"/>
     </row>
     <row r="53" ht="15" customHeight="1">
-      <c r="E53" s="1"/>
+      <c r="E53" s="3"/>
     </row>
     <row r="54" ht="15" customHeight="1">
-      <c r="E54" s="1"/>
+      <c r="E54" s="3"/>
     </row>
     <row r="55" ht="15" customHeight="1">
-      <c r="E55" s="1"/>
+      <c r="E55" s="3"/>
     </row>
     <row r="56" ht="15" customHeight="1">
-      <c r="E56" s="1"/>
+      <c r="E56" s="3"/>
     </row>
     <row r="57" ht="15" customHeight="1">
-      <c r="E57" s="1"/>
+      <c r="E57" s="3"/>
     </row>
     <row r="58" ht="15" customHeight="1">
-      <c r="E58" s="1"/>
+      <c r="E58" s="3"/>
     </row>
     <row r="59" ht="15" customHeight="1">
-      <c r="E59" s="1"/>
+      <c r="E59" s="3"/>
     </row>
     <row r="60" ht="15" customHeight="1">
-      <c r="E60" s="1"/>
+      <c r="E60" s="3"/>
     </row>
     <row r="61" ht="15" customHeight="1">
-      <c r="E61" s="1"/>
+      <c r="E61" s="3"/>
     </row>
     <row r="62" ht="15" customHeight="1">
-      <c r="E62" s="1"/>
+      <c r="E62" s="3"/>
     </row>
     <row r="63" ht="15" customHeight="1">
-      <c r="E63" s="1"/>
+      <c r="E63" s="3"/>
     </row>
     <row r="64" ht="15" customHeight="1">
-      <c r="E64" s="1"/>
+      <c r="E64" s="3"/>
     </row>
     <row r="65" ht="15" customHeight="1">
-      <c r="E65" s="1"/>
+      <c r="E65" s="3"/>
     </row>
     <row r="66" ht="15" customHeight="1">
-      <c r="E66" s="1"/>
+      <c r="E66" s="3"/>
     </row>
     <row r="67" ht="15" customHeight="1">
-      <c r="E67" s="1"/>
+      <c r="E67" s="3"/>
     </row>
     <row r="68" ht="15" customHeight="1">
-      <c r="E68" s="1"/>
+      <c r="E68" s="3"/>
     </row>
     <row r="69" ht="15" customHeight="1">
-      <c r="E69" s="1"/>
+      <c r="E69" s="3"/>
     </row>
     <row r="70" ht="15" customHeight="1">
-      <c r="E70" s="1"/>
+      <c r="E70" s="3"/>
     </row>
     <row r="71" ht="15" customHeight="1">
-      <c r="E71" s="1"/>
+      <c r="E71" s="3"/>
     </row>
     <row r="72" ht="15" customHeight="1">
-      <c r="E72" s="1"/>
+      <c r="E72" s="3"/>
     </row>
     <row r="73" ht="15" customHeight="1">
-      <c r="E73" s="1"/>
+      <c r="E73" s="3"/>
     </row>
     <row r="74" ht="15" customHeight="1">
-      <c r="E74" s="1"/>
+      <c r="E74" s="3"/>
     </row>
     <row r="75" ht="15" customHeight="1">
-      <c r="E75" s="1"/>
+      <c r="E75" s="3"/>
     </row>
     <row r="76" ht="15" customHeight="1">
-      <c r="E76" s="1"/>
+      <c r="E76" s="3"/>
     </row>
     <row r="77" ht="15" customHeight="1">
-      <c r="E77" s="1"/>
+      <c r="E77" s="3"/>
     </row>
     <row r="78" ht="15" customHeight="1">
-      <c r="E78" s="1"/>
+      <c r="E78" s="3"/>
     </row>
     <row r="79" ht="15" customHeight="1">
-      <c r="E79" s="1"/>
+      <c r="E79" s="3"/>
     </row>
     <row r="80" ht="15" customHeight="1">
-      <c r="E80" s="1"/>
+      <c r="E80" s="3"/>
     </row>
     <row r="81" ht="15" customHeight="1">
-      <c r="E81" s="1"/>
+      <c r="E81" s="3"/>
     </row>
     <row r="82" ht="15" customHeight="1">
-      <c r="E82" s="1"/>
+      <c r="E82" s="3"/>
     </row>
     <row r="83" ht="15" customHeight="1">
-      <c r="E83" s="1"/>
+      <c r="E83" s="3"/>
     </row>
     <row r="84" ht="15" customHeight="1">
-      <c r="E84" s="1"/>
+      <c r="E84" s="3"/>
     </row>
     <row r="85" ht="15" customHeight="1">
-      <c r="E85" s="1"/>
+      <c r="E85" s="3"/>
     </row>
     <row r="86" ht="15" customHeight="1">
-      <c r="E86" s="1"/>
+      <c r="E86" s="3"/>
     </row>
     <row r="87" ht="15" customHeight="1">
-      <c r="E87" s="1"/>
+      <c r="E87" s="3"/>
     </row>
     <row r="88" ht="15" customHeight="1">
-      <c r="E88" s="1"/>
+      <c r="E88" s="3"/>
     </row>
     <row r="89" ht="15" customHeight="1">
-      <c r="E89" s="1"/>
+      <c r="E89" s="3"/>
     </row>
     <row r="90" ht="15" customHeight="1">
-      <c r="E90" s="1"/>
+      <c r="E90" s="3"/>
     </row>
     <row r="91" ht="15" customHeight="1">
-      <c r="E91" s="1"/>
+      <c r="E91" s="3"/>
     </row>
     <row r="92" ht="15" customHeight="1">
-      <c r="E92" s="1"/>
+      <c r="E92" s="3"/>
     </row>
     <row r="93" ht="15" customHeight="1">
-      <c r="E93" s="1"/>
+      <c r="E93" s="3"/>
     </row>
     <row r="94" ht="15" customHeight="1">
-      <c r="E94" s="1"/>
+      <c r="E94" s="3"/>
     </row>
     <row r="95" ht="15" customHeight="1">
-      <c r="E95" s="1"/>
+      <c r="E95" s="3"/>
     </row>
     <row r="96" ht="15" customHeight="1">
-      <c r="E96" s="1"/>
+      <c r="E96" s="3"/>
     </row>
     <row r="97" ht="15" customHeight="1">
-      <c r="E97" s="1"/>
+      <c r="E97" s="3"/>
     </row>
     <row r="98" ht="15" customHeight="1">
-      <c r="E98" s="1"/>
+      <c r="E98" s="3"/>
     </row>
     <row r="99" ht="15" customHeight="1">
-      <c r="E99" s="1"/>
+      <c r="E99" s="3"/>
     </row>
     <row r="100" ht="15" customHeight="1">
-      <c r="E100" s="1"/>
+      <c r="E100" s="3"/>
     </row>
     <row r="101" ht="15" customHeight="1">
-      <c r="E101" s="1"/>
+      <c r="E101" s="3"/>
     </row>
     <row r="102" ht="15" customHeight="1">
-      <c r="E102" s="1"/>
+      <c r="E102" s="3"/>
     </row>
     <row r="103" ht="15" customHeight="1">
-      <c r="E103" s="1"/>
+      <c r="E103" s="3"/>
     </row>
     <row r="104" ht="15" customHeight="1">
-      <c r="E104" s="1"/>
+      <c r="E104" s="3"/>
     </row>
     <row r="105" ht="15" customHeight="1">
-      <c r="E105" s="1"/>
+      <c r="E105" s="3"/>
     </row>
     <row r="106" ht="15" customHeight="1">
-      <c r="E106" s="1"/>
+      <c r="E106" s="3"/>
     </row>
     <row r="107" ht="15" customHeight="1">
-      <c r="E107" s="1"/>
+      <c r="E107" s="3"/>
     </row>
     <row r="108" ht="15" customHeight="1">
-      <c r="E108" s="1"/>
+      <c r="E108" s="3"/>
     </row>
     <row r="109" ht="15" customHeight="1">
-      <c r="E109" s="1"/>
+      <c r="E109" s="3"/>
     </row>
     <row r="110" ht="15" customHeight="1">
-      <c r="E110" s="1"/>
+      <c r="E110" s="3"/>
     </row>
     <row r="111" ht="15" customHeight="1">
-      <c r="E111" s="1"/>
+      <c r="E111" s="3"/>
     </row>
     <row r="112" ht="15" customHeight="1">
-      <c r="E112" s="1"/>
+      <c r="E112" s="3"/>
     </row>
     <row r="113" ht="15" customHeight="1">
-      <c r="E113" s="1"/>
+      <c r="E113" s="3"/>
     </row>
     <row r="114" ht="15" customHeight="1">
-      <c r="E114" s="1"/>
+      <c r="E114" s="3"/>
     </row>
     <row r="115" ht="15" customHeight="1">
-      <c r="E115" s="1"/>
+      <c r="E115" s="3"/>
     </row>
     <row r="116" ht="15" customHeight="1">
-      <c r="E116" s="1"/>
+      <c r="E116" s="3"/>
     </row>
     <row r="117" ht="15" customHeight="1">
-      <c r="E117" s="1"/>
+      <c r="E117" s="3"/>
     </row>
     <row r="118" ht="15" customHeight="1">
-      <c r="E118" s="1"/>
+      <c r="E118" s="3"/>
     </row>
     <row r="119" ht="15" customHeight="1">
-      <c r="E119" s="1"/>
+      <c r="E119" s="3"/>
     </row>
     <row r="120" ht="15" customHeight="1">
-      <c r="E120" s="1"/>
+      <c r="E120" s="3"/>
     </row>
     <row r="121" ht="15" customHeight="1">
-      <c r="E121" s="1"/>
+      <c r="E121" s="3"/>
     </row>
     <row r="122" ht="15" customHeight="1">
-      <c r="E122" s="1"/>
+      <c r="E122" s="3"/>
     </row>
     <row r="123" ht="15" customHeight="1">
-      <c r="E123" s="1"/>
+      <c r="E123" s="3"/>
     </row>
     <row r="124" ht="15" customHeight="1">
-      <c r="E124" s="1"/>
+      <c r="E124" s="3"/>
     </row>
     <row r="125" ht="15" customHeight="1">
-      <c r="E125" s="1"/>
+      <c r="E125" s="3"/>
     </row>
     <row r="126" ht="15" customHeight="1">
-      <c r="E126" s="1"/>
+      <c r="E126" s="3"/>
     </row>
     <row r="127" ht="15" customHeight="1">
-      <c r="E127" s="1"/>
+      <c r="E127" s="3"/>
     </row>
     <row r="128" ht="15" customHeight="1">
-      <c r="E128" s="1"/>
+      <c r="E128" s="3"/>
     </row>
     <row r="129" ht="15" customHeight="1">
-      <c r="E129" s="1"/>
+      <c r="E129" s="3"/>
     </row>
     <row r="130" ht="15" customHeight="1">
-      <c r="E130" s="1"/>
+      <c r="E130" s="3"/>
     </row>
     <row r="131" ht="15" customHeight="1">
-      <c r="E131" s="1"/>
+      <c r="E131" s="3"/>
     </row>
     <row r="132" ht="15" customHeight="1">
-      <c r="E132" s="1"/>
+      <c r="E132" s="3"/>
     </row>
     <row r="133" ht="15" customHeight="1">
-      <c r="E133" s="1"/>
+      <c r="E133" s="3"/>
     </row>
     <row r="134" ht="15" customHeight="1">
-      <c r="E134" s="1"/>
+      <c r="E134" s="3"/>
     </row>
     <row r="135" ht="15" customHeight="1">
-      <c r="E135" s="1"/>
+      <c r="E135" s="3"/>
     </row>
     <row r="136" ht="15" customHeight="1">
-      <c r="E136" s="1"/>
+      <c r="E136" s="3"/>
     </row>
     <row r="137" ht="15" customHeight="1">
-      <c r="E137" s="1"/>
+      <c r="E137" s="3"/>
     </row>
     <row r="138" ht="15" customHeight="1">
-      <c r="E138" s="1"/>
+      <c r="E138" s="3"/>
     </row>
     <row r="139" ht="15" customHeight="1">
-      <c r="E139" s="1"/>
+      <c r="E139" s="3"/>
     </row>
     <row r="140" ht="15" customHeight="1">
-      <c r="E140" s="1"/>
+      <c r="E140" s="3"/>
     </row>
     <row r="141" ht="15" customHeight="1">
-      <c r="E141" s="1"/>
+      <c r="E141" s="3"/>
     </row>
     <row r="142" ht="15" customHeight="1">
-      <c r="E142" s="1"/>
+      <c r="E142" s="3"/>
     </row>
     <row r="143" ht="15" customHeight="1">
-      <c r="E143" s="1"/>
+      <c r="E143" s="3"/>
     </row>
     <row r="144" ht="15" customHeight="1">
-      <c r="E144" s="1"/>
+      <c r="E144" s="3"/>
     </row>
     <row r="145" ht="15" customHeight="1">
-      <c r="E145" s="1"/>
+      <c r="E145" s="3"/>
     </row>
     <row r="146" ht="15" customHeight="1">
-      <c r="E146" s="1"/>
+      <c r="E146" s="3"/>
     </row>
     <row r="147" ht="15" customHeight="1">
-      <c r="E147" s="1"/>
+      <c r="E147" s="3"/>
     </row>
     <row r="148" ht="15" customHeight="1">
-      <c r="E148" s="1"/>
+      <c r="E148" s="3"/>
     </row>
     <row r="149" ht="15" customHeight="1">
-      <c r="E149" s="1"/>
+      <c r="E149" s="3"/>
     </row>
     <row r="150" ht="15" customHeight="1">
-      <c r="E150" s="1"/>
+      <c r="E150" s="3"/>
     </row>
     <row r="151" ht="15" customHeight="1">
-      <c r="E151" s="1"/>
+      <c r="E151" s="3"/>
     </row>
     <row r="152" ht="15" customHeight="1">
-      <c r="E152" s="1"/>
+      <c r="E152" s="3"/>
     </row>
     <row r="153" ht="15" customHeight="1">
-      <c r="E153" s="1"/>
+      <c r="E153" s="3"/>
     </row>
     <row r="154" ht="15" customHeight="1">
-      <c r="E154" s="1"/>
+      <c r="E154" s="3"/>
     </row>
     <row r="155" ht="15" customHeight="1">
-      <c r="E155" s="1"/>
+      <c r="E155" s="3"/>
     </row>
     <row r="156" ht="15" customHeight="1">
-      <c r="E156" s="1"/>
+      <c r="E156" s="3"/>
     </row>
     <row r="157" ht="15" customHeight="1">
-      <c r="E157" s="1"/>
+      <c r="E157" s="3"/>
     </row>
     <row r="158" ht="15" customHeight="1">
-      <c r="E158" s="1"/>
+      <c r="E158" s="3"/>
     </row>
     <row r="159" ht="15" customHeight="1">
-      <c r="E159" s="1"/>
+      <c r="E159" s="3"/>
     </row>
     <row r="160" ht="15" customHeight="1">
-      <c r="E160" s="1"/>
+      <c r="E160" s="3"/>
     </row>
     <row r="161" ht="15" customHeight="1">
-      <c r="E161" s="1"/>
+      <c r="E161" s="3"/>
     </row>
     <row r="162" ht="15" customHeight="1">
-      <c r="E162" s="1"/>
+      <c r="E162" s="3"/>
     </row>
     <row r="163" ht="15" customHeight="1">
-      <c r="E163" s="1"/>
+      <c r="E163" s="3"/>
     </row>
     <row r="164" ht="15" customHeight="1">
-      <c r="E164" s="1"/>
+      <c r="E164" s="3"/>
     </row>
     <row r="165" ht="15" customHeight="1">
-      <c r="E165" s="1"/>
+      <c r="E165" s="3"/>
     </row>
     <row r="166" ht="15" customHeight="1">
-      <c r="E166" s="1"/>
+      <c r="E166" s="3"/>
     </row>
     <row r="167" ht="15" customHeight="1">
-      <c r="E167" s="1"/>
+      <c r="E167" s="3"/>
     </row>
     <row r="168" ht="15" customHeight="1">
-      <c r="E168" s="1"/>
+      <c r="E168" s="3"/>
     </row>
     <row r="169" ht="15" customHeight="1">
-      <c r="E169" s="1"/>
+      <c r="E169" s="3"/>
     </row>
     <row r="170" ht="15" customHeight="1">
-      <c r="E170" s="1"/>
+      <c r="E170" s="3"/>
     </row>
     <row r="171" ht="15" customHeight="1">
-      <c r="E171" s="1"/>
+      <c r="E171" s="3"/>
     </row>
     <row r="172" ht="15" customHeight="1">
-      <c r="E172" s="1"/>
+      <c r="E172" s="3"/>
     </row>
     <row r="173" ht="15" customHeight="1">
-      <c r="E173" s="1"/>
+      <c r="E173" s="3"/>
     </row>
     <row r="174" ht="15" customHeight="1">
-      <c r="E174" s="1"/>
+      <c r="E174" s="3"/>
     </row>
     <row r="175" ht="15" customHeight="1">
-      <c r="E175" s="1"/>
+      <c r="E175" s="3"/>
     </row>
     <row r="176" ht="15" customHeight="1">
-      <c r="E176" s="1"/>
+      <c r="E176" s="3"/>
     </row>
     <row r="177" ht="15" customHeight="1">
-      <c r="E177" s="1"/>
+      <c r="E177" s="3"/>
     </row>
     <row r="178" ht="15" customHeight="1">
-      <c r="E178" s="1"/>
+      <c r="E178" s="3"/>
     </row>
     <row r="179" ht="15" customHeight="1">
-      <c r="E179" s="1"/>
+      <c r="E179" s="3"/>
     </row>
     <row r="180" ht="15" customHeight="1">
-      <c r="E180" s="1"/>
+      <c r="E180" s="3"/>
     </row>
     <row r="181" ht="15" customHeight="1">
-      <c r="E181" s="1"/>
+      <c r="E181" s="3"/>
     </row>
     <row r="182" ht="15" customHeight="1">
-      <c r="E182" s="1"/>
+      <c r="E182" s="3"/>
     </row>
     <row r="183" ht="15" customHeight="1">
-      <c r="E183" s="1"/>
+      <c r="E183" s="3"/>
     </row>
     <row r="184" ht="15" customHeight="1">
-      <c r="E184" s="1"/>
+      <c r="E184" s="3"/>
     </row>
     <row r="185" ht="15" customHeight="1">
-      <c r="E185" s="1"/>
+      <c r="E185" s="3"/>
     </row>
     <row r="186" ht="15" customHeight="1">
-      <c r="E186" s="1"/>
+      <c r="E186" s="3"/>
     </row>
     <row r="187" ht="15" customHeight="1">
-      <c r="E187" s="1"/>
+      <c r="E187" s="3"/>
     </row>
     <row r="188" ht="15" customHeight="1">
-      <c r="E188" s="1"/>
+      <c r="E188" s="3"/>
     </row>
     <row r="189" ht="15" customHeight="1">
-      <c r="E189" s="1"/>
+      <c r="E189" s="3"/>
     </row>
     <row r="190" ht="15" customHeight="1">
-      <c r="E190" s="1"/>
+      <c r="E190" s="3"/>
     </row>
     <row r="191" ht="15" customHeight="1">
-      <c r="E191" s="1"/>
+      <c r="E191" s="3"/>
     </row>
     <row r="192" ht="15" customHeight="1">
-      <c r="E192" s="1"/>
+      <c r="E192" s="3"/>
     </row>
     <row r="193" ht="15" customHeight="1">
-      <c r="E193" s="1"/>
+      <c r="E193" s="3"/>
     </row>
     <row r="194" ht="15" customHeight="1">
-      <c r="E194" s="1"/>
+      <c r="E194" s="3"/>
     </row>
     <row r="195" ht="15" customHeight="1">
-      <c r="E195" s="1"/>
+      <c r="E195" s="3"/>
     </row>
     <row r="196" ht="15" customHeight="1">
-      <c r="E196" s="1"/>
+      <c r="E196" s="3"/>
     </row>
     <row r="197" ht="15" customHeight="1">
-      <c r="E197" s="1"/>
+      <c r="E197" s="3"/>
     </row>
     <row r="198" ht="15" customHeight="1">
-      <c r="E198" s="1"/>
+      <c r="E198" s="3"/>
     </row>
     <row r="199" ht="15" customHeight="1">
-      <c r="E199" s="1"/>
+      <c r="E199" s="3"/>
     </row>
     <row r="200" ht="15" customHeight="1">
-      <c r="E200" s="1"/>
+      <c r="E200" s="3"/>
     </row>
     <row r="201" ht="15" customHeight="1">
-      <c r="E201" s="1"/>
+      <c r="E201" s="3"/>
     </row>
     <row r="202" ht="15" customHeight="1">
-      <c r="E202" s="1"/>
+      <c r="E202" s="3"/>
     </row>
     <row r="203" ht="15" customHeight="1">
-      <c r="E203" s="1"/>
+      <c r="E203" s="3"/>
     </row>
     <row r="204" ht="15" customHeight="1">
-      <c r="E204" s="1"/>
+      <c r="E204" s="3"/>
     </row>
     <row r="205" ht="15" customHeight="1">
-      <c r="E205" s="1"/>
+      <c r="E205" s="3"/>
     </row>
     <row r="206" ht="15" customHeight="1">
-      <c r="E206" s="1"/>
+      <c r="E206" s="3"/>
     </row>
     <row r="207" ht="15" customHeight="1">
-      <c r="E207" s="1"/>
+      <c r="E207" s="3"/>
     </row>
     <row r="208" ht="15" customHeight="1">
-      <c r="E208" s="1"/>
+      <c r="E208" s="3"/>
     </row>
     <row r="209" ht="15" customHeight="1">
-      <c r="E209" s="1"/>
+      <c r="E209" s="3"/>
     </row>
     <row r="210" ht="15" customHeight="1">
-      <c r="E210" s="1"/>
+      <c r="E210" s="3"/>
     </row>
     <row r="211" ht="15" customHeight="1">
-      <c r="E211" s="1"/>
+      <c r="E211" s="3"/>
     </row>
     <row r="212" ht="15" customHeight="1">
-      <c r="E212" s="1"/>
+      <c r="E212" s="3"/>
     </row>
     <row r="213" ht="15" customHeight="1">
-      <c r="E213" s="1"/>
+      <c r="E213" s="3"/>
     </row>
     <row r="214" ht="15" customHeight="1">
-      <c r="E214" s="1"/>
+      <c r="E214" s="3"/>
     </row>
     <row r="215" ht="15" customHeight="1">
-      <c r="E215" s="1"/>
+      <c r="E215" s="3"/>
     </row>
     <row r="216" ht="15" customHeight="1">
-      <c r="E216" s="1"/>
+      <c r="E216" s="3"/>
     </row>
     <row r="217" ht="15" customHeight="1">
-      <c r="E217" s="1"/>
+      <c r="E217" s="3"/>
     </row>
     <row r="218" ht="15" customHeight="1">
-      <c r="E218" s="1"/>
+      <c r="E218" s="3"/>
     </row>
     <row r="219" ht="15" customHeight="1">
-      <c r="E219" s="1"/>
+      <c r="E219" s="3"/>
     </row>
     <row r="220" ht="15" customHeight="1">
-      <c r="E220" s="1"/>
+      <c r="E220" s="3"/>
     </row>
     <row r="221" ht="15" customHeight="1">
-      <c r="E221" s="1"/>
+      <c r="E221" s="3"/>
     </row>
     <row r="222" ht="15" customHeight="1">
-      <c r="E222" s="1"/>
+      <c r="E222" s="3"/>
     </row>
     <row r="223" ht="15" customHeight="1">
-      <c r="E223" s="1"/>
+      <c r="E223" s="3"/>
     </row>
     <row r="224" ht="15" customHeight="1">
-      <c r="E224" s="1"/>
+      <c r="E224" s="3"/>
     </row>
     <row r="225" ht="15" customHeight="1">
-      <c r="E225" s="1"/>
+      <c r="E225" s="3"/>
     </row>
     <row r="226" ht="15" customHeight="1">
-      <c r="E226" s="1"/>
+      <c r="E226" s="3"/>
     </row>
     <row r="227" ht="15" customHeight="1">
-      <c r="E227" s="1"/>
+      <c r="E227" s="3"/>
     </row>
     <row r="228" ht="15" customHeight="1">
-      <c r="E228" s="1"/>
+      <c r="E228" s="3"/>
     </row>
     <row r="229" ht="15" customHeight="1">
-      <c r="E229" s="1"/>
+      <c r="E229" s="3"/>
     </row>
     <row r="230" ht="15" customHeight="1">
-      <c r="E230" s="1"/>
+      <c r="E230" s="3"/>
     </row>
     <row r="231" ht="15" customHeight="1">
-      <c r="E231" s="1"/>
+      <c r="E231" s="3"/>
     </row>
     <row r="232" ht="15" customHeight="1">
-      <c r="E232" s="1"/>
+      <c r="E232" s="3"/>
     </row>
     <row r="233" ht="15" customHeight="1">
-      <c r="E233" s="1"/>
+      <c r="E233" s="3"/>
     </row>
     <row r="234" ht="15" customHeight="1">
-      <c r="E234" s="1"/>
+      <c r="E234" s="3"/>
     </row>
     <row r="235" ht="15" customHeight="1">
-      <c r="E235" s="1"/>
+      <c r="E235" s="3"/>
     </row>
     <row r="236" ht="15" customHeight="1">
-      <c r="E236" s="1"/>
+      <c r="E236" s="3"/>
     </row>
     <row r="237" ht="15" customHeight="1">
-      <c r="E237" s="1"/>
+      <c r="E237" s="3"/>
     </row>
     <row r="238" ht="15" customHeight="1">
-      <c r="E238" s="1"/>
+      <c r="E238" s="3"/>
     </row>
     <row r="239" ht="15" customHeight="1">
-      <c r="E239" s="1"/>
+      <c r="E239" s="3"/>
     </row>
     <row r="240" ht="15" customHeight="1">
-      <c r="E240" s="1"/>
+      <c r="E240" s="3"/>
     </row>
     <row r="241" ht="15" customHeight="1">
-      <c r="E241" s="1"/>
+      <c r="E241" s="3"/>
     </row>
     <row r="242" ht="15" customHeight="1">
-      <c r="E242" s="1"/>
+      <c r="E242" s="3"/>
     </row>
     <row r="243" ht="15" customHeight="1">
-      <c r="E243" s="1"/>
+      <c r="E243" s="3"/>
     </row>
     <row r="244" ht="15" customHeight="1">
-      <c r="E244" s="1"/>
+      <c r="E244" s="3"/>
     </row>
     <row r="245" ht="15" customHeight="1">
-      <c r="E245" s="1"/>
+      <c r="E245" s="3"/>
     </row>
     <row r="246" ht="15" customHeight="1">
-      <c r="E246" s="1"/>
+      <c r="E246" s="3"/>
     </row>
     <row r="247" ht="15" customHeight="1">
-      <c r="E247" s="1"/>
+      <c r="E247" s="3"/>
     </row>
     <row r="248" ht="15" customHeight="1">
-      <c r="E248" s="1"/>
+      <c r="E248" s="3"/>
     </row>
     <row r="249" ht="15" customHeight="1">
-      <c r="E249" s="1"/>
+      <c r="E249" s="3"/>
     </row>
     <row r="250" ht="15" customHeight="1">
-      <c r="E250" s="1"/>
+      <c r="E250" s="3"/>
     </row>
     <row r="251" ht="15" customHeight="1">
-      <c r="E251" s="1"/>
+      <c r="E251" s="3"/>
     </row>
     <row r="252" ht="15" customHeight="1">
-      <c r="E252" s="1"/>
+      <c r="E252" s="3"/>
     </row>
     <row r="253" ht="15" customHeight="1">
-      <c r="E253" s="1"/>
+      <c r="E253" s="3"/>
     </row>
     <row r="254" ht="15" customHeight="1">
-      <c r="E254" s="1"/>
+      <c r="E254" s="3"/>
     </row>
     <row r="255" ht="15" customHeight="1">
-      <c r="E255" s="1"/>
+      <c r="E255" s="3"/>
     </row>
     <row r="256" ht="15" customHeight="1">
-      <c r="E256" s="1"/>
+      <c r="E256" s="3"/>
     </row>
     <row r="257" ht="15" customHeight="1">
-      <c r="E257" s="1"/>
+      <c r="E257" s="3"/>
     </row>
     <row r="258" ht="15" customHeight="1">
-      <c r="E258" s="1"/>
+      <c r="E258" s="3"/>
     </row>
     <row r="259" ht="15" customHeight="1">
-      <c r="E259" s="1"/>
+      <c r="E259" s="3"/>
     </row>
     <row r="260" ht="15" customHeight="1">
-      <c r="E260" s="1"/>
+      <c r="E260" s="3"/>
     </row>
     <row r="261" ht="15" customHeight="1">
-      <c r="E261" s="1"/>
+      <c r="E261" s="3"/>
     </row>
     <row r="262" ht="15" customHeight="1">
-      <c r="E262" s="1"/>
+      <c r="E262" s="3"/>
     </row>
     <row r="263" ht="15" customHeight="1">
-      <c r="E263" s="1"/>
+      <c r="E263" s="3"/>
     </row>
     <row r="264" ht="15" customHeight="1">
-      <c r="E264" s="1"/>
+      <c r="E264" s="3"/>
     </row>
     <row r="265" ht="15" customHeight="1">
-      <c r="E265" s="1"/>
+      <c r="E265" s="3"/>
     </row>
     <row r="266" ht="15" customHeight="1">
-      <c r="E266" s="1"/>
+      <c r="E266" s="3"/>
     </row>
     <row r="267" ht="15" customHeight="1">
-      <c r="E267" s="1"/>
+      <c r="E267" s="3"/>
     </row>
     <row r="268" ht="15" customHeight="1">
-      <c r="E268" s="1"/>
+      <c r="E268" s="3"/>
     </row>
     <row r="269" ht="15" customHeight="1">
-      <c r="E269" s="1"/>
+      <c r="E269" s="3"/>
     </row>
     <row r="270" ht="15" customHeight="1">
-      <c r="E270" s="1"/>
+      <c r="E270" s="3"/>
     </row>
     <row r="271" ht="15" customHeight="1">
-      <c r="E271" s="1"/>
+      <c r="E271" s="3"/>
     </row>
     <row r="272" ht="15" customHeight="1">
-      <c r="E272" s="1"/>
+      <c r="E272" s="3"/>
     </row>
     <row r="273" ht="15" customHeight="1">
-      <c r="E273" s="1"/>
+      <c r="E273" s="3"/>
     </row>
     <row r="274" ht="15" customHeight="1">
-      <c r="E274" s="1"/>
+      <c r="E274" s="3"/>
     </row>
     <row r="275" ht="15" customHeight="1">
-      <c r="E275" s="1"/>
+      <c r="E275" s="3"/>
     </row>
     <row r="276" ht="15" customHeight="1">
-      <c r="E276" s="1"/>
+      <c r="E276" s="3"/>
     </row>
     <row r="277" ht="15" customHeight="1">
-      <c r="E277" s="1"/>
+      <c r="E277" s="3"/>
     </row>
     <row r="278" ht="15" customHeight="1">
-      <c r="E278" s="1"/>
+      <c r="E278" s="3"/>
     </row>
     <row r="279" ht="15" customHeight="1">
-      <c r="E279" s="1"/>
+      <c r="E279" s="3"/>
     </row>
     <row r="280" ht="15" customHeight="1">
-      <c r="E280" s="1"/>
+      <c r="E280" s="3"/>
     </row>
     <row r="281" ht="15" customHeight="1">
-      <c r="E281" s="1"/>
+      <c r="E281" s="3"/>
     </row>
     <row r="282" ht="15" customHeight="1">
-      <c r="E282" s="1"/>
+      <c r="E282" s="3"/>
     </row>
     <row r="283" ht="15" customHeight="1">
-      <c r="E283" s="1"/>
+      <c r="E283" s="3"/>
     </row>
     <row r="284" ht="15" customHeight="1">
-      <c r="E284" s="1"/>
+      <c r="E284" s="3"/>
     </row>
     <row r="285" ht="15" customHeight="1">
-      <c r="E285" s="1"/>
+      <c r="E285" s="3"/>
     </row>
     <row r="286" ht="15" customHeight="1">
-      <c r="E286" s="1"/>
+      <c r="E286" s="3"/>
     </row>
     <row r="287" ht="15" customHeight="1">
-      <c r="E287" s="1"/>
+      <c r="E287" s="3"/>
     </row>
     <row r="288" ht="15" customHeight="1">
-      <c r="E288" s="1"/>
+      <c r="E288" s="3"/>
     </row>
     <row r="289" ht="15" customHeight="1">
-      <c r="E289" s="1"/>
+      <c r="E289" s="3"/>
     </row>
     <row r="290" ht="15" customHeight="1">
-      <c r="E290" s="1"/>
+      <c r="E290" s="3"/>
     </row>
     <row r="291" ht="15" customHeight="1">
-      <c r="E291" s="1"/>
+      <c r="E291" s="3"/>
     </row>
     <row r="292" ht="15" customHeight="1">
-      <c r="E292" s="1"/>
+      <c r="E292" s="3"/>
     </row>
     <row r="293" ht="15" customHeight="1">
-      <c r="E293" s="1"/>
+      <c r="E293" s="3"/>
     </row>
     <row r="294" ht="15" customHeight="1">
-      <c r="E294" s="1"/>
+      <c r="E294" s="3"/>
     </row>
     <row r="295" ht="15" customHeight="1">
-      <c r="E295" s="1"/>
+      <c r="E295" s="3"/>
     </row>
     <row r="296" ht="15" customHeight="1">
-      <c r="E296" s="1"/>
+      <c r="E296" s="3"/>
     </row>
     <row r="297" ht="15" customHeight="1">
-      <c r="E297" s="1"/>
+      <c r="E297" s="3"/>
     </row>
     <row r="298" ht="15" customHeight="1">
-      <c r="E298" s="1"/>
+      <c r="E298" s="3"/>
     </row>
     <row r="299" ht="15" customHeight="1">
-      <c r="E299" s="1"/>
+      <c r="E299" s="3"/>
     </row>
     <row r="300" ht="15" customHeight="1">
-      <c r="E300" s="1"/>
+      <c r="E300" s="3"/>
     </row>
     <row r="301" ht="15" customHeight="1">
-      <c r="E301" s="1"/>
+      <c r="E301" s="3"/>
     </row>
     <row r="302" ht="15" customHeight="1">
-      <c r="E302" s="1"/>
+      <c r="E302" s="3"/>
     </row>
     <row r="303" ht="15" customHeight="1">
-      <c r="E303" s="1"/>
+      <c r="E303" s="3"/>
     </row>
     <row r="304" ht="15" customHeight="1">
-      <c r="E304" s="1"/>
+      <c r="E304" s="3"/>
     </row>
     <row r="305" ht="15" customHeight="1">
-      <c r="E305" s="1"/>
+      <c r="E305" s="3"/>
     </row>
     <row r="306" ht="15" customHeight="1">
-      <c r="E306" s="1"/>
+      <c r="E306" s="3"/>
     </row>
     <row r="307" ht="15" customHeight="1">
-      <c r="E307" s="1"/>
+      <c r="E307" s="3"/>
     </row>
     <row r="308" ht="15" customHeight="1">
-      <c r="E308" s="1"/>
+      <c r="E308" s="3"/>
     </row>
     <row r="309" ht="15" customHeight="1">
-      <c r="E309" s="1"/>
+      <c r="E309" s="3"/>
     </row>
     <row r="310" ht="15" customHeight="1">
-      <c r="E310" s="1"/>
+      <c r="E310" s="3"/>
     </row>
     <row r="311" ht="15" customHeight="1">
-      <c r="E311" s="1"/>
+      <c r="E311" s="3"/>
     </row>
     <row r="312" ht="15" customHeight="1">
-      <c r="E312" s="1"/>
+      <c r="E312" s="3"/>
     </row>
     <row r="313" ht="15" customHeight="1">
-      <c r="E313" s="1"/>
+      <c r="E313" s="3"/>
     </row>
     <row r="314" ht="15" customHeight="1">
-      <c r="E314" s="1"/>
+      <c r="E314" s="3"/>
     </row>
     <row r="315" ht="15" customHeight="1">
-      <c r="E315" s="1"/>
+      <c r="E315" s="3"/>
     </row>
     <row r="316" ht="15" customHeight="1">
-      <c r="E316" s="1"/>
+      <c r="E316" s="3"/>
     </row>
     <row r="317" ht="15" customHeight="1">
-      <c r="E317" s="1"/>
+      <c r="E317" s="3"/>
     </row>
     <row r="318" ht="15" customHeight="1">
-      <c r="E318" s="1"/>
+      <c r="E318" s="3"/>
     </row>
     <row r="319" ht="15" customHeight="1">
-      <c r="E319" s="1"/>
+      <c r="E319" s="3"/>
     </row>
     <row r="320" ht="15" customHeight="1">
-      <c r="E320" s="1"/>
+      <c r="E320" s="3"/>
     </row>
     <row r="321" ht="15" customHeight="1">
-      <c r="E321" s="1"/>
+      <c r="E321" s="3"/>
     </row>
     <row r="322" ht="15" customHeight="1">
-      <c r="E322" s="1"/>
+      <c r="E322" s="3"/>
     </row>
     <row r="323" ht="15" customHeight="1">
-      <c r="E323" s="1"/>
+      <c r="E323" s="3"/>
     </row>
     <row r="324" ht="15" customHeight="1">
-      <c r="E324" s="1"/>
+      <c r="E324" s="3"/>
     </row>
     <row r="325" ht="15" customHeight="1">
-      <c r="E325" s="1"/>
+      <c r="E325" s="3"/>
     </row>
     <row r="326" ht="15" customHeight="1">
-      <c r="E326" s="1"/>
+      <c r="E326" s="3"/>
     </row>
     <row r="327" ht="15" customHeight="1">
-      <c r="E327" s="1"/>
+      <c r="E327" s="3"/>
     </row>
     <row r="328" ht="15" customHeight="1">
-      <c r="E328" s="1"/>
+      <c r="E328" s="3"/>
     </row>
     <row r="329" ht="15" customHeight="1">
-      <c r="E329" s="1"/>
+      <c r="E329" s="3"/>
     </row>
     <row r="330" ht="15" customHeight="1">
-      <c r="E330" s="1"/>
+      <c r="E330" s="3"/>
     </row>
     <row r="331" ht="15" customHeight="1">
-      <c r="E331" s="1"/>
+      <c r="E331" s="3"/>
     </row>
     <row r="332" ht="15" customHeight="1">
-      <c r="E332" s="1"/>
+      <c r="E332" s="3"/>
     </row>
     <row r="333" ht="15" customHeight="1">
-      <c r="E333" s="1"/>
+      <c r="E333" s="3"/>
     </row>
     <row r="334" ht="15" customHeight="1">
-      <c r="E334" s="1"/>
+      <c r="E334" s="3"/>
     </row>
     <row r="335" ht="15" customHeight="1">
-      <c r="E335" s="1"/>
+      <c r="E335" s="3"/>
     </row>
     <row r="336" ht="15" customHeight="1">
-      <c r="E336" s="1"/>
+      <c r="E336" s="3"/>
     </row>
     <row r="337" ht="15" customHeight="1">
-      <c r="E337" s="1"/>
+      <c r="E337" s="3"/>
     </row>
     <row r="338" ht="15" customHeight="1">
-      <c r="E338" s="1"/>
+      <c r="E338" s="3"/>
     </row>
     <row r="339" ht="15" customHeight="1">
-      <c r="E339" s="1"/>
+      <c r="E339" s="3"/>
     </row>
     <row r="340" ht="15" customHeight="1">
-      <c r="E340" s="1"/>
+      <c r="E340" s="3"/>
     </row>
     <row r="341" ht="15" customHeight="1">
-      <c r="E341" s="1"/>
+      <c r="E341" s="3"/>
     </row>
     <row r="342" ht="15" customHeight="1">
-      <c r="E342" s="1"/>
+      <c r="E342" s="3"/>
     </row>
     <row r="343" ht="15" customHeight="1">
-      <c r="E343" s="1"/>
+      <c r="E343" s="3"/>
     </row>
     <row r="344" ht="15" customHeight="1">
-      <c r="E344" s="1"/>
+      <c r="E344" s="3"/>
     </row>
     <row r="345" ht="15" customHeight="1">
-      <c r="E345" s="1"/>
+      <c r="E345" s="3"/>
     </row>
     <row r="346" ht="15" customHeight="1">
-      <c r="E346" s="1"/>
+      <c r="E346" s="3"/>
     </row>
     <row r="347" ht="15" customHeight="1">
-      <c r="E347" s="1"/>
+      <c r="E347" s="3"/>
     </row>
     <row r="348" ht="15" customHeight="1">
-      <c r="E348" s="1"/>
+      <c r="E348" s="3"/>
     </row>
     <row r="349" ht="15" customHeight="1">
-      <c r="E349" s="1"/>
+      <c r="E349" s="3"/>
     </row>
     <row r="350" ht="15" customHeight="1">
-      <c r="E350" s="1"/>
+      <c r="E350" s="3"/>
     </row>
     <row r="351" ht="15" customHeight="1">
-      <c r="E351" s="1"/>
+      <c r="E351" s="3"/>
     </row>
     <row r="352" ht="15" customHeight="1">
-      <c r="E352" s="1"/>
+      <c r="E352" s="3"/>
     </row>
     <row r="353" ht="15" customHeight="1">
-      <c r="E353" s="1"/>
+      <c r="E353" s="3"/>
     </row>
     <row r="354" ht="15" customHeight="1">
-      <c r="E354" s="1"/>
+      <c r="E354" s="3"/>
     </row>
     <row r="355" ht="15" customHeight="1">
-      <c r="E355" s="1"/>
+      <c r="E355" s="3"/>
     </row>
     <row r="356" ht="15" customHeight="1">
-      <c r="E356" s="1"/>
+      <c r="E356" s="3"/>
     </row>
     <row r="357" ht="15" customHeight="1">
-      <c r="E357" s="1"/>
+      <c r="E357" s="3"/>
     </row>
     <row r="358" ht="15" customHeight="1">
-      <c r="E358" s="1"/>
+      <c r="E358" s="3"/>
     </row>
     <row r="359" ht="15" customHeight="1">
-      <c r="E359" s="1"/>
+      <c r="E359" s="3"/>
     </row>
     <row r="360" ht="15" customHeight="1">
-      <c r="E360" s="1"/>
+      <c r="E360" s="3"/>
     </row>
     <row r="361" ht="15" customHeight="1">
-      <c r="E361" s="1"/>
+      <c r="E361" s="3"/>
     </row>
     <row r="362" ht="15" customHeight="1">
-      <c r="E362" s="1"/>
+      <c r="E362" s="3"/>
     </row>
     <row r="363" ht="15" customHeight="1">
-      <c r="E363" s="1"/>
+      <c r="E363" s="3"/>
     </row>
     <row r="364" ht="15" customHeight="1">
-      <c r="E364" s="1"/>
+      <c r="E364" s="3"/>
     </row>
     <row r="365" ht="15" customHeight="1">
-      <c r="E365" s="1"/>
+      <c r="E365" s="3"/>
     </row>
     <row r="366" ht="15" customHeight="1">
-      <c r="E366" s="1"/>
+      <c r="E366" s="3"/>
     </row>
     <row r="367" ht="15" customHeight="1">
-      <c r="E367" s="1"/>
+      <c r="E367" s="3"/>
     </row>
     <row r="368" ht="15" customHeight="1">
-      <c r="E368" s="1"/>
+      <c r="E368" s="3"/>
     </row>
     <row r="369" ht="15" customHeight="1">
-      <c r="E369" s="1"/>
+      <c r="E369" s="3"/>
     </row>
     <row r="370" ht="15" customHeight="1">
-      <c r="E370" s="1"/>
+      <c r="E370" s="3"/>
     </row>
     <row r="371" ht="15" customHeight="1">
-      <c r="E371" s="1"/>
+      <c r="E371" s="3"/>
     </row>
     <row r="372" ht="15" customHeight="1">
-      <c r="E372" s="1"/>
+      <c r="E372" s="3"/>
     </row>
     <row r="373" ht="15" customHeight="1">
-      <c r="E373" s="1"/>
+      <c r="E373" s="3"/>
     </row>
     <row r="374" ht="15" customHeight="1">
-      <c r="E374" s="1"/>
+      <c r="E374" s="3"/>
     </row>
     <row r="375" ht="15" customHeight="1">
-      <c r="E375" s="1"/>
+      <c r="E375" s="3"/>
     </row>
     <row r="376" ht="15" customHeight="1">
-      <c r="E376" s="1"/>
+      <c r="E376" s="3"/>
     </row>
     <row r="377" ht="15" customHeight="1">
-      <c r="E377" s="1"/>
+      <c r="E377" s="3"/>
     </row>
     <row r="378" ht="15" customHeight="1">
-      <c r="E378" s="1"/>
+      <c r="E378" s="3"/>
     </row>
     <row r="379" ht="15" customHeight="1">
-      <c r="E379" s="1"/>
+      <c r="E379" s="3"/>
     </row>
     <row r="380" ht="15" customHeight="1">
-      <c r="E380" s="1"/>
+      <c r="E380" s="3"/>
     </row>
     <row r="381" ht="15" customHeight="1">
-      <c r="E381" s="1"/>
+      <c r="E381" s="3"/>
     </row>
     <row r="382" ht="15" customHeight="1">
-      <c r="E382" s="1"/>
+      <c r="E382" s="3"/>
     </row>
     <row r="383" ht="15" customHeight="1">
-      <c r="E383" s="1"/>
+      <c r="E383" s="3"/>
     </row>
     <row r="384" ht="15" customHeight="1">
-      <c r="E384" s="1"/>
+      <c r="E384" s="3"/>
     </row>
     <row r="385" ht="15" customHeight="1">
-      <c r="E385" s="1"/>
+      <c r="E385" s="3"/>
     </row>
     <row r="386" ht="15" customHeight="1">
-      <c r="E386" s="1"/>
+      <c r="E386" s="3"/>
     </row>
     <row r="387" ht="15" customHeight="1">
-      <c r="E387" s="1"/>
+      <c r="E387" s="3"/>
     </row>
     <row r="388" ht="15" customHeight="1">
-      <c r="E388" s="1"/>
+      <c r="E388" s="3"/>
     </row>
     <row r="389" ht="15" customHeight="1">
-      <c r="E389" s="1"/>
+      <c r="E389" s="3"/>
     </row>
     <row r="390" ht="15" customHeight="1">
-      <c r="E390" s="1"/>
+      <c r="E390" s="3"/>
     </row>
     <row r="391" ht="15" customHeight="1">
-      <c r="E391" s="1"/>
+      <c r="E391" s="3"/>
     </row>
     <row r="392" ht="15" customHeight="1">
-      <c r="E392" s="1"/>
+      <c r="E392" s="3"/>
     </row>
     <row r="393" ht="15" customHeight="1">
-      <c r="E393" s="1"/>
+      <c r="E393" s="3"/>
     </row>
     <row r="394" ht="15" customHeight="1">
-      <c r="E394" s="1"/>
+      <c r="E394" s="3"/>
     </row>
     <row r="395" ht="15" customHeight="1">
-      <c r="E395" s="1"/>
+      <c r="E395" s="3"/>
     </row>
     <row r="396" ht="15" customHeight="1">
-      <c r="E396" s="1"/>
+      <c r="E396" s="3"/>
     </row>
     <row r="397" ht="15" customHeight="1">
-      <c r="E397" s="1"/>
+      <c r="E397" s="3"/>
     </row>
     <row r="398" ht="15" customHeight="1">
-      <c r="E398" s="1"/>
+      <c r="E398" s="3"/>
     </row>
     <row r="399" ht="15" customHeight="1">
-      <c r="E399" s="1"/>
+      <c r="E399" s="3"/>
     </row>
     <row r="400" ht="15" customHeight="1">
-      <c r="E400" s="1"/>
+      <c r="E400" s="3"/>
     </row>
     <row r="401" ht="15" customHeight="1">
-      <c r="E401" s="1"/>
+      <c r="E401" s="3"/>
     </row>
     <row r="402" ht="15" customHeight="1">
-      <c r="E402" s="1"/>
+      <c r="E402" s="3"/>
     </row>
     <row r="403" ht="15" customHeight="1">
-      <c r="E403" s="1"/>
+      <c r="E403" s="3"/>
     </row>
     <row r="404" ht="15" customHeight="1">
-      <c r="E404" s="1"/>
+      <c r="E404" s="3"/>
     </row>
     <row r="405" ht="15" customHeight="1">
-      <c r="E405" s="1"/>
+      <c r="E405" s="3"/>
     </row>
     <row r="406" ht="15" customHeight="1">
-      <c r="E406" s="1"/>
+      <c r="E406" s="3"/>
     </row>
     <row r="407" ht="15" customHeight="1">
-      <c r="E407" s="1"/>
+      <c r="E407" s="3"/>
     </row>
     <row r="408" ht="15" customHeight="1">
-      <c r="E408" s="1"/>
+      <c r="E408" s="3"/>
     </row>
     <row r="409" ht="15" customHeight="1">
-      <c r="E409" s="1"/>
+      <c r="E409" s="3"/>
     </row>
     <row r="410" ht="15" customHeight="1">
-      <c r="E410" s="1"/>
+      <c r="E410" s="3"/>
     </row>
     <row r="411" ht="15" customHeight="1">
-      <c r="E411" s="1"/>
+      <c r="E411" s="3"/>
     </row>
     <row r="412" ht="15" customHeight="1">
-      <c r="E412" s="1"/>
+      <c r="E412" s="3"/>
     </row>
     <row r="413" ht="15" customHeight="1">
-      <c r="E413" s="1"/>
+      <c r="E413" s="3"/>
     </row>
     <row r="414" ht="15" customHeight="1">
-      <c r="E414" s="1"/>
+      <c r="E414" s="3"/>
     </row>
     <row r="415" ht="15" customHeight="1">
-      <c r="E415" s="1"/>
+      <c r="E415" s="3"/>
     </row>
     <row r="416" ht="15" customHeight="1">
-      <c r="E416" s="1"/>
+      <c r="E416" s="3"/>
     </row>
     <row r="417" ht="15" customHeight="1">
-      <c r="E417" s="1"/>
+      <c r="E417" s="3"/>
     </row>
     <row r="418" ht="15" customHeight="1">
-      <c r="E418" s="1"/>
+      <c r="E418" s="3"/>
     </row>
     <row r="419" ht="15" customHeight="1">
-      <c r="E419" s="1"/>
+      <c r="E419" s="3"/>
     </row>
     <row r="420" ht="15" customHeight="1">
-      <c r="E420" s="1"/>
+      <c r="E420" s="3"/>
     </row>
     <row r="421" ht="15" customHeight="1">
-      <c r="E421" s="1"/>
+      <c r="E421" s="3"/>
     </row>
     <row r="422" ht="15" customHeight="1">
-      <c r="E422" s="1"/>
+      <c r="E422" s="3"/>
     </row>
     <row r="423" ht="15" customHeight="1">
-      <c r="E423" s="1"/>
+      <c r="E423" s="3"/>
     </row>
     <row r="424" ht="15" customHeight="1">
-      <c r="E424" s="1"/>
+      <c r="E424" s="3"/>
     </row>
     <row r="425" ht="15" customHeight="1">
-      <c r="E425" s="1"/>
+      <c r="E425" s="3"/>
     </row>
     <row r="426" ht="15" customHeight="1">
-      <c r="E426" s="1"/>
+      <c r="E426" s="3"/>
     </row>
     <row r="427" ht="15" customHeight="1">
-      <c r="E427" s="1"/>
+      <c r="E427" s="3"/>
     </row>
     <row r="428" ht="15" customHeight="1">
-      <c r="E428" s="1"/>
+      <c r="E428" s="3"/>
     </row>
     <row r="429" ht="15" customHeight="1">
-      <c r="E429" s="1"/>
+      <c r="E429" s="3"/>
     </row>
     <row r="430" ht="15" customHeight="1">
-      <c r="E430" s="1"/>
+      <c r="E430" s="3"/>
     </row>
     <row r="431" ht="15" customHeight="1">
-      <c r="E431" s="1"/>
+      <c r="E431" s="3"/>
     </row>
     <row r="432" ht="15" customHeight="1">
-      <c r="E432" s="1"/>
+      <c r="E432" s="3"/>
     </row>
     <row r="433" ht="15" customHeight="1">
-      <c r="E433" s="1"/>
+      <c r="E433" s="3"/>
     </row>
     <row r="434" ht="15" customHeight="1">
-      <c r="E434" s="1"/>
+      <c r="E434" s="3"/>
     </row>
     <row r="435" ht="15" customHeight="1">
-      <c r="E435" s="1"/>
+      <c r="E435" s="3"/>
     </row>
     <row r="436" ht="15" customHeight="1">
-      <c r="E436" s="1"/>
+      <c r="E436" s="3"/>
     </row>
     <row r="437" ht="15" customHeight="1">
-      <c r="E437" s="1"/>
+      <c r="E437" s="3"/>
     </row>
     <row r="438" ht="15" customHeight="1">
-      <c r="E438" s="1"/>
+      <c r="E438" s="3"/>
     </row>
     <row r="439" ht="15" customHeight="1">
-      <c r="E439" s="1"/>
+      <c r="E439" s="3"/>
     </row>
     <row r="440" ht="15" customHeight="1">
-      <c r="E440" s="1"/>
+      <c r="E440" s="3"/>
     </row>
     <row r="441" ht="15" customHeight="1">
-      <c r="E441" s="1"/>
+      <c r="E441" s="3"/>
     </row>
     <row r="442" ht="15" customHeight="1">
-      <c r="E442" s="1"/>
+      <c r="E442" s="3"/>
     </row>
     <row r="443" ht="15" customHeight="1">
-      <c r="E443" s="1"/>
+      <c r="E443" s="3"/>
     </row>
     <row r="444" ht="15" customHeight="1">
-      <c r="E444" s="1"/>
+      <c r="E444" s="3"/>
     </row>
     <row r="445" ht="15" customHeight="1">
-      <c r="E445" s="1"/>
+      <c r="E445" s="3"/>
     </row>
     <row r="446" ht="15" customHeight="1">
-      <c r="E446" s="1"/>
+      <c r="E446" s="3"/>
     </row>
     <row r="447" ht="15" customHeight="1">
-      <c r="E447" s="1"/>
+      <c r="E447" s="3"/>
     </row>
     <row r="448" ht="15" customHeight="1">
-      <c r="E448" s="1"/>
+      <c r="E448" s="3"/>
     </row>
     <row r="449" ht="15" customHeight="1">
-      <c r="E449" s="1"/>
+      <c r="E449" s="3"/>
     </row>
     <row r="450" ht="15" customHeight="1">
-      <c r="E450" s="1"/>
+      <c r="E450" s="3"/>
     </row>
     <row r="451" ht="15" customHeight="1">
-      <c r="E451" s="1"/>
+      <c r="E451" s="3"/>
     </row>
     <row r="452" ht="15" customHeight="1">
-      <c r="E452" s="1"/>
+      <c r="E452" s="3"/>
     </row>
     <row r="453" ht="15" customHeight="1">
-      <c r="E453" s="1"/>
+      <c r="E453" s="3"/>
     </row>
     <row r="454" ht="15" customHeight="1">
-      <c r="E454" s="1"/>
+      <c r="E454" s="3"/>
     </row>
     <row r="455" ht="15" customHeight="1">
-      <c r="E455" s="1"/>
+      <c r="E455" s="3"/>
     </row>
     <row r="456" ht="15" customHeight="1">
-      <c r="E456" s="1"/>
+      <c r="E456" s="3"/>
     </row>
     <row r="457" ht="15" customHeight="1">
-      <c r="E457" s="1"/>
+      <c r="E457" s="3"/>
     </row>
     <row r="458" ht="15" customHeight="1">
-      <c r="E458" s="1"/>
+      <c r="E458" s="3"/>
     </row>
     <row r="459" ht="15" customHeight="1">
-      <c r="E459" s="1"/>
+      <c r="E459" s="3"/>
     </row>
     <row r="460" ht="15" customHeight="1">
-      <c r="E460" s="1"/>
+      <c r="E460" s="3"/>
     </row>
     <row r="461" ht="15" customHeight="1">
-      <c r="E461" s="1"/>
+      <c r="E461" s="3"/>
     </row>
     <row r="462" ht="15" customHeight="1">
-      <c r="E462" s="1"/>
+      <c r="E462" s="3"/>
     </row>
     <row r="463" ht="15" customHeight="1">
-      <c r="E463" s="1"/>
+      <c r="E463" s="3"/>
     </row>
     <row r="464" ht="15" customHeight="1">
-      <c r="E464" s="1"/>
+      <c r="E464" s="3"/>
     </row>
     <row r="465" ht="15" customHeight="1">
-      <c r="E465" s="1"/>
+      <c r="E465" s="3"/>
     </row>
     <row r="466" ht="15" customHeight="1">
-      <c r="E466" s="1"/>
+      <c r="E466" s="3"/>
     </row>
     <row r="467" ht="15" customHeight="1">
-      <c r="E467" s="1"/>
+      <c r="E467" s="3"/>
     </row>
     <row r="468" ht="15" customHeight="1">
-      <c r="E468" s="1"/>
+      <c r="E468" s="3"/>
     </row>
     <row r="469" ht="15" customHeight="1">
-      <c r="E469" s="1"/>
+      <c r="E469" s="3"/>
     </row>
     <row r="470" ht="15" customHeight="1">
-      <c r="E470" s="1"/>
+      <c r="E470" s="3"/>
     </row>
     <row r="471" ht="15" customHeight="1">
-      <c r="E471" s="1"/>
+      <c r="E471" s="3"/>
     </row>
     <row r="472" ht="15" customHeight="1">
-      <c r="E472" s="1"/>
+      <c r="E472" s="3"/>
     </row>
     <row r="473" ht="15" customHeight="1">
-      <c r="E473" s="1"/>
+      <c r="E473" s="3"/>
     </row>
     <row r="474" ht="15" customHeight="1">
-      <c r="E474" s="1"/>
+      <c r="E474" s="3"/>
     </row>
     <row r="475" ht="15" customHeight="1">
-      <c r="E475" s="1"/>
+      <c r="E475" s="3"/>
     </row>
     <row r="476" ht="15" customHeight="1">
-      <c r="E476" s="1"/>
+      <c r="E476" s="3"/>
     </row>
     <row r="477" ht="15" customHeight="1">
-      <c r="E477" s="1"/>
+      <c r="E477" s="3"/>
     </row>
     <row r="478" ht="15" customHeight="1">
-      <c r="E478" s="1"/>
+      <c r="E478" s="3"/>
     </row>
     <row r="479" ht="15" customHeight="1">
-      <c r="E479" s="1"/>
+      <c r="E479" s="3"/>
     </row>
     <row r="480" ht="15" customHeight="1">
-      <c r="E480" s="1"/>
+      <c r="E480" s="3"/>
     </row>
     <row r="481" ht="15" customHeight="1">
-      <c r="E481" s="1"/>
+      <c r="E481" s="3"/>
     </row>
     <row r="482" ht="15" customHeight="1">
-      <c r="E482" s="1"/>
+      <c r="E482" s="3"/>
     </row>
     <row r="483" ht="15" customHeight="1">
-      <c r="E483" s="1"/>
+      <c r="E483" s="3"/>
     </row>
     <row r="484" ht="15" customHeight="1">
-      <c r="E484" s="1"/>
+      <c r="E484" s="3"/>
     </row>
     <row r="485" ht="15" customHeight="1">
-      <c r="E485" s="1"/>
+      <c r="E485" s="3"/>
     </row>
     <row r="486" ht="15" customHeight="1">
-      <c r="E486" s="1"/>
+      <c r="E486" s="3"/>
     </row>
     <row r="487" ht="15" customHeight="1">
-      <c r="E487" s="1"/>
+      <c r="E487" s="3"/>
     </row>
     <row r="488" ht="15" customHeight="1">
-      <c r="E488" s="1"/>
+      <c r="E488" s="3"/>
     </row>
     <row r="489" ht="15" customHeight="1">
-      <c r="E489" s="1"/>
+      <c r="E489" s="3"/>
     </row>
     <row r="490" ht="15" customHeight="1">
-      <c r="E490" s="1"/>
+      <c r="E490" s="3"/>
     </row>
     <row r="491" ht="15" customHeight="1">
-      <c r="E491" s="1"/>
+      <c r="E491" s="3"/>
     </row>
     <row r="492" ht="15" customHeight="1">
-      <c r="E492" s="1"/>
+      <c r="E492" s="3"/>
     </row>
     <row r="493" ht="15" customHeight="1">
-      <c r="E493" s="1"/>
+      <c r="E493" s="3"/>
     </row>
     <row r="494" ht="15" customHeight="1">
-      <c r="E494" s="1"/>
+      <c r="E494" s="3"/>
     </row>
     <row r="495" ht="15" customHeight="1">
-      <c r="E495" s="1"/>
+      <c r="E495" s="3"/>
     </row>
     <row r="496" ht="15" customHeight="1">
-      <c r="E496" s="1"/>
+      <c r="E496" s="3"/>
     </row>
     <row r="497" ht="15" customHeight="1">
-      <c r="E497" s="1"/>
+      <c r="E497" s="3"/>
     </row>
     <row r="498" ht="15" customHeight="1">
-      <c r="E498" s="1"/>
+      <c r="E498" s="3"/>
     </row>
     <row r="499" ht="15" customHeight="1">
-      <c r="E499" s="1"/>
+      <c r="E499" s="3"/>
     </row>
     <row r="500" ht="15" customHeight="1">
-      <c r="E500" s="1"/>
+      <c r="E500" s="3"/>
     </row>
     <row r="501" ht="15" customHeight="1">
-      <c r="E501" s="1"/>
+      <c r="E501" s="3"/>
     </row>
     <row r="502" ht="15" customHeight="1">
-      <c r="E502" s="1"/>
+      <c r="E502" s="3"/>
     </row>
     <row r="503" ht="15" customHeight="1">
-      <c r="E503" s="1"/>
+      <c r="E503" s="3"/>
     </row>
     <row r="504" ht="15" customHeight="1">
-      <c r="E504" s="1"/>
+      <c r="E504" s="3"/>
     </row>
     <row r="505" ht="15" customHeight="1">
-      <c r="E505" s="1"/>
+      <c r="E505" s="3"/>
     </row>
     <row r="506" ht="15" customHeight="1">
-      <c r="E506" s="1"/>
+      <c r="E506" s="3"/>
     </row>
     <row r="507" ht="15" customHeight="1">
-      <c r="E507" s="1"/>
+      <c r="E507" s="3"/>
     </row>
     <row r="508" ht="15" customHeight="1">
-      <c r="E508" s="1"/>
+      <c r="E508" s="3"/>
     </row>
     <row r="509" ht="15" customHeight="1">
-      <c r="E509" s="1"/>
+      <c r="E509" s="3"/>
     </row>
     <row r="510" ht="15" customHeight="1">
-      <c r="E510" s="1"/>
+      <c r="E510" s="3"/>
     </row>
     <row r="511" ht="15" customHeight="1">
-      <c r="E511" s="1"/>
+      <c r="E511" s="3"/>
     </row>
     <row r="512" ht="15" customHeight="1">
-      <c r="E512" s="1"/>
+      <c r="E512" s="3"/>
     </row>
     <row r="513" ht="15" customHeight="1">
-      <c r="E513" s="1"/>
+      <c r="E513" s="3"/>
     </row>
     <row r="514" ht="15" customHeight="1">
-      <c r="E514" s="1"/>
+      <c r="E514" s="3"/>
     </row>
     <row r="515" ht="15" customHeight="1">
-      <c r="E515" s="1"/>
+      <c r="E515" s="3"/>
     </row>
     <row r="516" ht="15" customHeight="1">
-      <c r="E516" s="1"/>
+      <c r="E516" s="3"/>
     </row>
     <row r="517" ht="15" customHeight="1">
-      <c r="E517" s="1"/>
+      <c r="E517" s="3"/>
     </row>
     <row r="518" ht="15" customHeight="1">
-      <c r="E518" s="1"/>
+      <c r="E518" s="3"/>
     </row>
     <row r="519" ht="15" customHeight="1">
-      <c r="E519" s="1"/>
+      <c r="E519" s="3"/>
     </row>
     <row r="520" ht="15" customHeight="1">
-      <c r="E520" s="1"/>
+      <c r="E520" s="3"/>
     </row>
     <row r="521" ht="15" customHeight="1">
-      <c r="E521" s="1"/>
+      <c r="E521" s="3"/>
     </row>
     <row r="522" ht="15" customHeight="1">
-      <c r="E522" s="1"/>
+      <c r="E522" s="3"/>
     </row>
     <row r="523" ht="15" customHeight="1">
-      <c r="E523" s="1"/>
+      <c r="E523" s="3"/>
     </row>
     <row r="524" ht="15" customHeight="1">
-      <c r="E524" s="1"/>
+      <c r="E524" s="3"/>
     </row>
     <row r="525" ht="15" customHeight="1">
-      <c r="E525" s="1"/>
+      <c r="E525" s="3"/>
     </row>
     <row r="526" ht="15" customHeight="1">
-      <c r="E526" s="1"/>
+      <c r="E526" s="3"/>
     </row>
     <row r="527" ht="15" customHeight="1">
-      <c r="E527" s="1"/>
+      <c r="E527" s="3"/>
     </row>
     <row r="528" ht="15" customHeight="1">
-      <c r="E528" s="1"/>
+      <c r="E528" s="3"/>
     </row>
     <row r="529" ht="15" customHeight="1">
-      <c r="E529" s="1"/>
+      <c r="E529" s="3"/>
     </row>
     <row r="530" ht="15" customHeight="1">
-      <c r="E530" s="1"/>
+      <c r="E530" s="3"/>
     </row>
     <row r="531" ht="15" customHeight="1">
-      <c r="E531" s="1"/>
+      <c r="E531" s="3"/>
     </row>
     <row r="532" ht="15" customHeight="1">
-      <c r="E532" s="1"/>
+      <c r="E532" s="3"/>
     </row>
     <row r="533" ht="15" customHeight="1">
-      <c r="E533" s="1"/>
+      <c r="E533" s="3"/>
     </row>
     <row r="534" ht="15" customHeight="1">
-      <c r="E534" s="1"/>
+      <c r="E534" s="3"/>
     </row>
     <row r="535" ht="15" customHeight="1">
-      <c r="E535" s="1"/>
+      <c r="E535" s="3"/>
     </row>
     <row r="536" ht="15" customHeight="1">
-      <c r="E536" s="1"/>
+      <c r="E536" s="3"/>
     </row>
     <row r="537" ht="15" customHeight="1">
-      <c r="E537" s="1"/>
+      <c r="E537" s="3"/>
     </row>
     <row r="538" ht="15" customHeight="1">
-      <c r="E538" s="1"/>
+      <c r="E538" s="3"/>
     </row>
     <row r="539" ht="15" customHeight="1">
-      <c r="E539" s="1"/>
+      <c r="E539" s="3"/>
     </row>
     <row r="540" ht="15" customHeight="1">
-      <c r="E540" s="1"/>
+      <c r="E540" s="3"/>
     </row>
     <row r="541" ht="15" customHeight="1">
-      <c r="E541" s="1"/>
+      <c r="E541" s="3"/>
     </row>
     <row r="542" ht="15" customHeight="1">
-      <c r="E542" s="1"/>
+      <c r="E542" s="3"/>
     </row>
     <row r="543" ht="15" customHeight="1">
-      <c r="E543" s="1"/>
+      <c r="E543" s="3"/>
     </row>
     <row r="544" ht="15" customHeight="1">
-      <c r="E544" s="1"/>
+      <c r="E544" s="3"/>
     </row>
     <row r="545" ht="15" customHeight="1">
-      <c r="E545" s="1"/>
+      <c r="E545" s="3"/>
     </row>
     <row r="546" ht="15" customHeight="1">
-      <c r="E546" s="1"/>
+      <c r="E546" s="3"/>
     </row>
     <row r="547" ht="15" customHeight="1">
-      <c r="E547" s="1"/>
+      <c r="E547" s="3"/>
     </row>
     <row r="548" ht="15" customHeight="1">
-      <c r="E548" s="1"/>
+      <c r="E548" s="3"/>
     </row>
     <row r="549" ht="15" customHeight="1">
-      <c r="E549" s="1"/>
+      <c r="E549" s="3"/>
     </row>
     <row r="550" ht="15" customHeight="1">
-      <c r="E550" s="1"/>
+      <c r="E550" s="3"/>
     </row>
     <row r="551" ht="15" customHeight="1">
-      <c r="E551" s="1"/>
+      <c r="E551" s="3"/>
     </row>
     <row r="552" ht="15" customHeight="1">
-      <c r="E552" s="1"/>
+      <c r="E552" s="3"/>
     </row>
     <row r="553" ht="15" customHeight="1">
-      <c r="E553" s="1"/>
+      <c r="E553" s="3"/>
     </row>
     <row r="554" ht="15" customHeight="1">
-      <c r="E554" s="1"/>
+      <c r="E554" s="3"/>
     </row>
     <row r="555" ht="15" customHeight="1">
-      <c r="E555" s="1"/>
+      <c r="E555" s="3"/>
     </row>
     <row r="556" ht="15" customHeight="1">
-      <c r="E556" s="1"/>
+      <c r="E556" s="3"/>
     </row>
     <row r="557" ht="15" customHeight="1">
-      <c r="E557" s="1"/>
+      <c r="E557" s="3"/>
     </row>
     <row r="558" ht="15" customHeight="1">
-      <c r="E558" s="1"/>
+      <c r="E558" s="3"/>
     </row>
     <row r="559" ht="15" customHeight="1">
-      <c r="E559" s="1"/>
+      <c r="E559" s="3"/>
     </row>
     <row r="560" ht="15" customHeight="1">
-      <c r="E560" s="1"/>
+      <c r="E560" s="3"/>
     </row>
     <row r="561" ht="15" customHeight="1">
-      <c r="E561" s="1"/>
+      <c r="E561" s="3"/>
     </row>
     <row r="562" ht="15" customHeight="1">
-      <c r="E562" s="1"/>
+      <c r="E562" s="3"/>
     </row>
     <row r="563" ht="15" customHeight="1">
-      <c r="E563" s="1"/>
+      <c r="E563" s="3"/>
     </row>
     <row r="564" ht="15" customHeight="1">
-      <c r="E564" s="1"/>
+      <c r="E564" s="3"/>
     </row>
     <row r="565" ht="15" customHeight="1">
-      <c r="E565" s="1"/>
+      <c r="E565" s="3"/>
     </row>
     <row r="566" ht="15" customHeight="1">
-      <c r="E566" s="1"/>
+      <c r="E566" s="3"/>
     </row>
     <row r="567" ht="15" customHeight="1">
-      <c r="E567" s="1"/>
+      <c r="E567" s="3"/>
     </row>
     <row r="568" ht="15" customHeight="1">
-      <c r="E568" s="1"/>
+      <c r="E568" s="3"/>
     </row>
     <row r="569" ht="15" customHeight="1">
-      <c r="E569" s="1"/>
+      <c r="E569" s="3"/>
     </row>
     <row r="570" ht="15" customHeight="1">
-      <c r="E570" s="1"/>
+      <c r="E570" s="3"/>
     </row>
     <row r="571" ht="15" customHeight="1">
-      <c r="E571" s="1"/>
+      <c r="E571" s="3"/>
     </row>
     <row r="572" ht="15" customHeight="1">
-      <c r="E572" s="1"/>
+      <c r="E572" s="3"/>
     </row>
     <row r="573" ht="15" customHeight="1">
-      <c r="E573" s="1"/>
+      <c r="E573" s="3"/>
     </row>
     <row r="574" ht="15" customHeight="1">
-      <c r="E574" s="1"/>
+      <c r="E574" s="3"/>
     </row>
     <row r="575" ht="15" customHeight="1">
-      <c r="E575" s="1"/>
+      <c r="E575" s="3"/>
     </row>
     <row r="576" ht="15" customHeight="1">
-      <c r="E576" s="1"/>
+      <c r="E576" s="3"/>
     </row>
     <row r="577" ht="15" customHeight="1">
-      <c r="E577" s="1"/>
+      <c r="E577" s="3"/>
     </row>
     <row r="578" ht="15" customHeight="1">
-      <c r="E578" s="1"/>
+      <c r="E578" s="3"/>
     </row>
     <row r="579" ht="15" customHeight="1">
-      <c r="E579" s="1"/>
+      <c r="E579" s="3"/>
     </row>
     <row r="580" ht="15" customHeight="1">
-      <c r="E580" s="1"/>
+      <c r="E580" s="3"/>
     </row>
     <row r="581" ht="15" customHeight="1">
-      <c r="E581" s="1"/>
+      <c r="E581" s="3"/>
     </row>
     <row r="582" ht="15" customHeight="1">
-      <c r="E582" s="1"/>
+      <c r="E582" s="3"/>
     </row>
     <row r="583" ht="15" customHeight="1">
-      <c r="E583" s="1"/>
+      <c r="E583" s="3"/>
     </row>
     <row r="584" ht="15" customHeight="1">
-      <c r="E584" s="1"/>
+      <c r="E584" s="3"/>
     </row>
     <row r="585" ht="15" customHeight="1">
-      <c r="E585" s="1"/>
+      <c r="E585" s="3"/>
     </row>
     <row r="586" ht="15" customHeight="1">
-      <c r="E586" s="1"/>
+      <c r="E586" s="3"/>
     </row>
     <row r="587" ht="15" customHeight="1">
-      <c r="E587" s="1"/>
+      <c r="E587" s="3"/>
     </row>
     <row r="588" ht="15" customHeight="1">
-      <c r="E588" s="1"/>
+      <c r="E588" s="3"/>
     </row>
     <row r="589" ht="15" customHeight="1">
-      <c r="E589" s="1"/>
+      <c r="E589" s="3"/>
     </row>
     <row r="590" ht="15" customHeight="1">
-      <c r="E590" s="1"/>
+      <c r="E590" s="3"/>
     </row>
     <row r="591" ht="15" customHeight="1">
-      <c r="E591" s="1"/>
+      <c r="E591" s="3"/>
     </row>
     <row r="592" ht="15" customHeight="1">
-      <c r="E592" s="1"/>
+      <c r="E592" s="3"/>
     </row>
     <row r="593" ht="15" customHeight="1">
-      <c r="E593" s="1"/>
+      <c r="E593" s="3"/>
     </row>
     <row r="594" ht="15" customHeight="1">
-      <c r="E594" s="1"/>
+      <c r="E594" s="3"/>
     </row>
     <row r="595" ht="15" customHeight="1">
-      <c r="E595" s="1"/>
+      <c r="E595" s="3"/>
     </row>
     <row r="596" ht="15" customHeight="1">
-      <c r="E596" s="1"/>
+      <c r="E596" s="3"/>
     </row>
     <row r="597" ht="15" customHeight="1">
-      <c r="E597" s="1"/>
+      <c r="E597" s="3"/>
     </row>
     <row r="598" ht="15" customHeight="1">
-      <c r="E598" s="1"/>
+      <c r="E598" s="3"/>
     </row>
     <row r="599" ht="15" customHeight="1">
-      <c r="E599" s="1"/>
+      <c r="E599" s="3"/>
     </row>
     <row r="600" ht="15" customHeight="1">
-      <c r="E600" s="1"/>
+      <c r="E600" s="3"/>
     </row>
     <row r="601" ht="15" customHeight="1">
-      <c r="E601" s="1"/>
+      <c r="E601" s="3"/>
     </row>
     <row r="602" ht="15" customHeight="1">
-      <c r="E602" s="1"/>
+      <c r="E602" s="3"/>
     </row>
     <row r="603" ht="15" customHeight="1">
-      <c r="E603" s="1"/>
+      <c r="E603" s="3"/>
     </row>
     <row r="604" ht="15" customHeight="1">
-      <c r="E604" s="1"/>
+      <c r="E604" s="3"/>
     </row>
     <row r="605" ht="15" customHeight="1">
-      <c r="E605" s="1"/>
+      <c r="E605" s="3"/>
     </row>
     <row r="606" ht="15" customHeight="1">
-      <c r="E606" s="1"/>
+      <c r="E606" s="3"/>
     </row>
     <row r="607" ht="15" customHeight="1">
-      <c r="E607" s="1"/>
+      <c r="E607" s="3"/>
     </row>
     <row r="608" ht="15" customHeight="1">
-      <c r="E608" s="1"/>
+      <c r="E608" s="3"/>
     </row>
     <row r="609" ht="15" customHeight="1">
-      <c r="E609" s="1"/>
+      <c r="E609" s="3"/>
     </row>
     <row r="610" ht="15" customHeight="1">
-      <c r="E610" s="1"/>
+      <c r="E610" s="3"/>
     </row>
     <row r="611" ht="15" customHeight="1">
-      <c r="E611" s="1"/>
+      <c r="E611" s="3"/>
     </row>
     <row r="612" ht="15" customHeight="1">
-      <c r="E612" s="1"/>
+      <c r="E612" s="3"/>
     </row>
     <row r="613" ht="15" customHeight="1">
-      <c r="E613" s="1"/>
+      <c r="E613" s="3"/>
     </row>
     <row r="614" ht="15" customHeight="1">
-      <c r="E614" s="1"/>
+      <c r="E614" s="3"/>
     </row>
     <row r="615" ht="15" customHeight="1">
-      <c r="E615" s="1"/>
+      <c r="E615" s="3"/>
     </row>
     <row r="616" ht="15" customHeight="1">
-      <c r="E616" s="1"/>
+      <c r="E616" s="3"/>
     </row>
     <row r="617" ht="15" customHeight="1">
-      <c r="E617" s="1"/>
+      <c r="E617" s="3"/>
     </row>
     <row r="618" ht="15" customHeight="1">
-      <c r="E618" s="1"/>
+      <c r="E618" s="3"/>
     </row>
     <row r="619" ht="15" customHeight="1">
-      <c r="E619" s="1"/>
+      <c r="E619" s="3"/>
     </row>
     <row r="620" ht="15" customHeight="1">
-      <c r="E620" s="1"/>
+      <c r="E620" s="3"/>
     </row>
     <row r="621" ht="15" customHeight="1">
-      <c r="E621" s="1"/>
+      <c r="E621" s="3"/>
     </row>
     <row r="622" ht="15" customHeight="1">
-      <c r="E622" s="1"/>
+      <c r="E622" s="3"/>
     </row>
     <row r="623" ht="15" customHeight="1">
-      <c r="E623" s="1"/>
+      <c r="E623" s="3"/>
     </row>
     <row r="624" ht="15" customHeight="1">
-      <c r="E624" s="1"/>
+      <c r="E624" s="3"/>
     </row>
     <row r="625" ht="15" customHeight="1">
-      <c r="E625" s="1"/>
+      <c r="E625" s="3"/>
     </row>
     <row r="626" ht="15" customHeight="1">
-      <c r="E626" s="1"/>
+      <c r="E626" s="3"/>
     </row>
     <row r="627" ht="15" customHeight="1">
-      <c r="E627" s="1"/>
+      <c r="E627" s="3"/>
     </row>
     <row r="628" ht="15" customHeight="1">
-      <c r="E628" s="1"/>
+      <c r="E628" s="3"/>
     </row>
     <row r="629" ht="15" customHeight="1">
-      <c r="E629" s="1"/>
+      <c r="E629" s="3"/>
     </row>
     <row r="630" ht="15" customHeight="1">
-      <c r="E630" s="1"/>
+      <c r="E630" s="3"/>
     </row>
     <row r="631" ht="15" customHeight="1">
-      <c r="E631" s="1"/>
+      <c r="E631" s="3"/>
     </row>
     <row r="632" ht="15" customHeight="1">
-      <c r="E632" s="1"/>
+      <c r="E632" s="3"/>
     </row>
     <row r="633" ht="15" customHeight="1">
-      <c r="E633" s="1"/>
+      <c r="E633" s="3"/>
     </row>
     <row r="634" ht="15" customHeight="1">
-      <c r="E634" s="1"/>
+      <c r="E634" s="3"/>
     </row>
     <row r="635" ht="15" customHeight="1">
-      <c r="E635" s="1"/>
+      <c r="E635" s="3"/>
     </row>
     <row r="636" ht="15" customHeight="1">
-      <c r="E636" s="1"/>
+      <c r="E636" s="3"/>
     </row>
     <row r="637" ht="15" customHeight="1">
-      <c r="E637" s="1"/>
+      <c r="E637" s="3"/>
     </row>
     <row r="638" ht="15" customHeight="1">
-      <c r="E638" s="1"/>
+      <c r="E638" s="3"/>
     </row>
     <row r="639" ht="15" customHeight="1">
-      <c r="E639" s="1"/>
+      <c r="E639" s="3"/>
     </row>
     <row r="640" ht="15" customHeight="1">
-      <c r="E640" s="1"/>
+      <c r="E640" s="3"/>
     </row>
     <row r="641" ht="15" customHeight="1">
-      <c r="E641" s="1"/>
+      <c r="E641" s="3"/>
     </row>
     <row r="642" ht="15" customHeight="1">
-      <c r="E642" s="1"/>
+      <c r="E642" s="3"/>
     </row>
     <row r="643" ht="15" customHeight="1">
-      <c r="E643" s="1"/>
+      <c r="E643" s="3"/>
     </row>
     <row r="644" ht="15" customHeight="1">
-      <c r="E644" s="1"/>
+      <c r="E644" s="3"/>
     </row>
     <row r="645" ht="15" customHeight="1">
-      <c r="E645" s="1"/>
+      <c r="E645" s="3"/>
     </row>
     <row r="646" ht="15" customHeight="1">
-      <c r="E646" s="1"/>
+      <c r="E646" s="3"/>
     </row>
     <row r="647" ht="15" customHeight="1">
-      <c r="E647" s="1"/>
+      <c r="E647" s="3"/>
     </row>
     <row r="648" ht="15" customHeight="1">
-      <c r="E648" s="1"/>
+      <c r="E648" s="3"/>
     </row>
     <row r="649" ht="15" customHeight="1">
-      <c r="E649" s="1"/>
+      <c r="E649" s="3"/>
     </row>
     <row r="650" ht="15" customHeight="1">
-      <c r="E650" s="1"/>
+      <c r="E650" s="3"/>
     </row>
     <row r="651" ht="15" customHeight="1">
-      <c r="E651" s="1"/>
+      <c r="E651" s="3"/>
     </row>
     <row r="652" ht="15" customHeight="1">
-      <c r="E652" s="1"/>
+      <c r="E652" s="3"/>
     </row>
     <row r="653" ht="15" customHeight="1">
-      <c r="E653" s="1"/>
+      <c r="E653" s="3"/>
     </row>
     <row r="654" ht="15" customHeight="1">
-      <c r="E654" s="1"/>
+      <c r="E654" s="3"/>
     </row>
     <row r="655" ht="15" customHeight="1">
-      <c r="E655" s="1"/>
+      <c r="E655" s="3"/>
     </row>
     <row r="656" ht="15" customHeight="1">
-      <c r="E656" s="1"/>
+      <c r="E656" s="3"/>
     </row>
     <row r="657" ht="15" customHeight="1">
-      <c r="E657" s="1"/>
+      <c r="E657" s="3"/>
     </row>
     <row r="658" ht="15" customHeight="1">
-      <c r="E658" s="1"/>
+      <c r="E658" s="3"/>
     </row>
     <row r="659" ht="15" customHeight="1">
-      <c r="E659" s="1"/>
+      <c r="E659" s="3"/>
     </row>
     <row r="660" ht="15" customHeight="1">
-      <c r="E660" s="1"/>
+      <c r="E660" s="3"/>
     </row>
     <row r="661" ht="15" customHeight="1">
-      <c r="E661" s="1"/>
+      <c r="E661" s="3"/>
     </row>
     <row r="662" ht="15" customHeight="1">
-      <c r="E662" s="1"/>
+      <c r="E662" s="3"/>
     </row>
     <row r="663" ht="15" customHeight="1">
-      <c r="E663" s="1"/>
+      <c r="E663" s="3"/>
     </row>
     <row r="664" ht="15" customHeight="1">
-      <c r="E664" s="1"/>
+      <c r="E664" s="3"/>
     </row>
     <row r="665" ht="15" customHeight="1">
-      <c r="E665" s="1"/>
+      <c r="E665" s="3"/>
     </row>
     <row r="666" ht="15" customHeight="1">
-      <c r="E666" s="1"/>
+      <c r="E666" s="3"/>
     </row>
     <row r="667" ht="15" customHeight="1">
-      <c r="E667" s="1"/>
+      <c r="E667" s="3"/>
     </row>
     <row r="668" ht="15" customHeight="1">
-      <c r="E668" s="1"/>
+      <c r="E668" s="3"/>
     </row>
     <row r="669" ht="15" customHeight="1">
-      <c r="E669" s="1"/>
+      <c r="E669" s="3"/>
     </row>
     <row r="670" ht="15" customHeight="1">
-      <c r="E670" s="1"/>
+      <c r="E670" s="3"/>
     </row>
     <row r="671" ht="15" customHeight="1">
-      <c r="E671" s="1"/>
+      <c r="E671" s="3"/>
     </row>
     <row r="672" ht="15" customHeight="1">
-      <c r="E672" s="1"/>
+      <c r="E672" s="3"/>
     </row>
     <row r="673" ht="15" customHeight="1">
-      <c r="E673" s="1"/>
+      <c r="E673" s="3"/>
     </row>
     <row r="674" ht="15" customHeight="1">
-      <c r="E674" s="1"/>
+      <c r="E674" s="3"/>
     </row>
     <row r="675" ht="15" customHeight="1">
-      <c r="E675" s="1"/>
+      <c r="E675" s="3"/>
     </row>
     <row r="676" ht="15" customHeight="1">
-      <c r="E676" s="1"/>
+      <c r="E676" s="3"/>
     </row>
     <row r="677" ht="15" customHeight="1">
-      <c r="E677" s="1"/>
+      <c r="E677" s="3"/>
     </row>
     <row r="678" ht="15" customHeight="1">
-      <c r="E678" s="1"/>
+      <c r="E678" s="3"/>
     </row>
     <row r="679" ht="15" customHeight="1">
-      <c r="E679" s="1"/>
+      <c r="E679" s="3"/>
     </row>
     <row r="680" ht="15" customHeight="1">
-      <c r="E680" s="1"/>
+      <c r="E680" s="3"/>
     </row>
     <row r="681" ht="15" customHeight="1">
-      <c r="E681" s="1"/>
+      <c r="E681" s="3"/>
     </row>
     <row r="682" ht="15" customHeight="1">
-      <c r="E682" s="1"/>
+      <c r="E682" s="3"/>
     </row>
     <row r="683" ht="15" customHeight="1">
-      <c r="E683" s="1"/>
+      <c r="E683" s="3"/>
     </row>
     <row r="684" ht="15" customHeight="1">
-      <c r="E684" s="1"/>
+      <c r="E684" s="3"/>
     </row>
     <row r="685" ht="15" customHeight="1">
-      <c r="E685" s="1"/>
+      <c r="E685" s="3"/>
     </row>
     <row r="686" ht="15" customHeight="1">
-      <c r="E686" s="1"/>
+      <c r="E686" s="3"/>
     </row>
     <row r="687" ht="15" customHeight="1">
-      <c r="E687" s="1"/>
+      <c r="E687" s="3"/>
     </row>
     <row r="688" ht="15" customHeight="1">
-      <c r="E688" s="1"/>
+      <c r="E688" s="3"/>
     </row>
     <row r="689" ht="15" customHeight="1">
-      <c r="E689" s="1"/>
+      <c r="E689" s="3"/>
     </row>
     <row r="690" ht="15" customHeight="1">
-      <c r="E690" s="1"/>
+      <c r="E690" s="3"/>
     </row>
     <row r="691" ht="15" customHeight="1">
-      <c r="E691" s="1"/>
+      <c r="E691" s="3"/>
     </row>
     <row r="692" ht="15" customHeight="1">
-      <c r="E692" s="1"/>
+      <c r="E692" s="3"/>
     </row>
     <row r="693" ht="15" customHeight="1">
-      <c r="E693" s="1"/>
+      <c r="E693" s="3"/>
     </row>
     <row r="694" ht="15" customHeight="1">
-      <c r="E694" s="1"/>
+      <c r="E694" s="3"/>
     </row>
     <row r="695" ht="15" customHeight="1">
-      <c r="E695" s="1"/>
+      <c r="E695" s="3"/>
     </row>
     <row r="696" ht="15" customHeight="1">
-      <c r="E696" s="1"/>
+      <c r="E696" s="3"/>
     </row>
     <row r="697" ht="15" customHeight="1">
-      <c r="E697" s="1"/>
+      <c r="E697" s="3"/>
     </row>
     <row r="698" ht="15" customHeight="1">
-      <c r="E698" s="1"/>
+      <c r="E698" s="3"/>
     </row>
     <row r="699" ht="15" customHeight="1">
-      <c r="E699" s="1"/>
+      <c r="E699" s="3"/>
     </row>
     <row r="700" ht="15" customHeight="1">
-      <c r="E700" s="1"/>
+      <c r="E700" s="3"/>
     </row>
     <row r="701" ht="15" customHeight="1">
-      <c r="E701" s="1"/>
+      <c r="E701" s="3"/>
     </row>
     <row r="702" ht="15" customHeight="1">
-      <c r="E702" s="1"/>
+      <c r="E702" s="3"/>
     </row>
     <row r="703" ht="15" customHeight="1">
-      <c r="E703" s="1"/>
+      <c r="E703" s="3"/>
     </row>
     <row r="704" ht="15" customHeight="1">
-      <c r="E704" s="1"/>
+      <c r="E704" s="3"/>
     </row>
     <row r="705" ht="15" customHeight="1">
-      <c r="E705" s="1"/>
+      <c r="E705" s="3"/>
     </row>
     <row r="706" ht="15" customHeight="1">
-      <c r="E706" s="1"/>
+      <c r="E706" s="3"/>
     </row>
     <row r="707" ht="15" customHeight="1">
-      <c r="E707" s="1"/>
+      <c r="E707" s="3"/>
     </row>
     <row r="708" ht="15" customHeight="1">
-      <c r="E708" s="1"/>
+      <c r="E708" s="3"/>
     </row>
     <row r="709" ht="15" customHeight="1">
-      <c r="E709" s="1"/>
+      <c r="E709" s="3"/>
     </row>
     <row r="710" ht="15" customHeight="1">
-      <c r="E710" s="1"/>
+      <c r="E710" s="3"/>
     </row>
     <row r="711" ht="15" customHeight="1">
-      <c r="E711" s="1"/>
+      <c r="E711" s="3"/>
     </row>
     <row r="712" ht="15" customHeight="1">
-      <c r="E712" s="1"/>
+      <c r="E712" s="3"/>
     </row>
     <row r="713" ht="15" customHeight="1">
-      <c r="E713" s="1"/>
+      <c r="E713" s="3"/>
     </row>
     <row r="714" ht="15" customHeight="1">
-      <c r="E714" s="1"/>
+      <c r="E714" s="3"/>
     </row>
     <row r="715" ht="15" customHeight="1">
-      <c r="E715" s="1"/>
+      <c r="E715" s="3"/>
     </row>
     <row r="716" ht="15" customHeight="1">
-      <c r="E716" s="1"/>
+      <c r="E716" s="3"/>
     </row>
     <row r="717" ht="15" customHeight="1">
-      <c r="E717" s="1"/>
+      <c r="E717" s="3"/>
     </row>
     <row r="718" ht="15" customHeight="1">
-      <c r="E718" s="1"/>
+      <c r="E718" s="3"/>
     </row>
     <row r="719" ht="15" customHeight="1">
-      <c r="E719" s="1"/>
+      <c r="E719" s="3"/>
     </row>
     <row r="720" ht="15" customHeight="1">
-      <c r="E720" s="1"/>
+      <c r="E720" s="3"/>
     </row>
     <row r="721" ht="15" customHeight="1">
-      <c r="E721" s="1"/>
+      <c r="E721" s="3"/>
     </row>
     <row r="722" ht="15" customHeight="1">
-      <c r="E722" s="1"/>
+      <c r="E722" s="3"/>
     </row>
     <row r="723" ht="15" customHeight="1">
-      <c r="E723" s="1"/>
+      <c r="E723" s="3"/>
     </row>
     <row r="724" ht="15" customHeight="1">
-      <c r="E724" s="1"/>
+      <c r="E724" s="3"/>
     </row>
     <row r="725" ht="15" customHeight="1">
-      <c r="E725" s="1"/>
+      <c r="E725" s="3"/>
     </row>
     <row r="726" ht="15" customHeight="1">
-      <c r="E726" s="1"/>
+      <c r="E726" s="3"/>
     </row>
     <row r="727" ht="15" customHeight="1">
-      <c r="E727" s="1"/>
+      <c r="E727" s="3"/>
     </row>
     <row r="728" ht="15" customHeight="1">
-      <c r="E728" s="1"/>
+      <c r="E728" s="3"/>
     </row>
     <row r="729" ht="15" customHeight="1">
-      <c r="E729" s="1"/>
+      <c r="E729" s="3"/>
     </row>
     <row r="730" ht="15" customHeight="1">
-      <c r="E730" s="1"/>
+      <c r="E730" s="3"/>
     </row>
     <row r="731" ht="15" customHeight="1">
-      <c r="E731" s="1"/>
+      <c r="E731" s="3"/>
     </row>
     <row r="732" ht="15" customHeight="1">
-      <c r="E732" s="1"/>
+      <c r="E732" s="3"/>
     </row>
     <row r="733" ht="15" customHeight="1">
-      <c r="E733" s="1"/>
+      <c r="E733" s="3"/>
     </row>
     <row r="734" ht="15" customHeight="1">
-      <c r="E734" s="1"/>
+      <c r="E734" s="3"/>
     </row>
     <row r="735" ht="15" customHeight="1">
-      <c r="E735" s="1"/>
+      <c r="E735" s="3"/>
     </row>
     <row r="736" ht="15" customHeight="1">
-      <c r="E736" s="1"/>
+      <c r="E736" s="3"/>
     </row>
     <row r="737" ht="15" customHeight="1">
-      <c r="E737" s="1"/>
+      <c r="E737" s="3"/>
     </row>
     <row r="738" ht="15" customHeight="1">
-      <c r="E738" s="1"/>
+      <c r="E738" s="3"/>
     </row>
     <row r="739" ht="15" customHeight="1">
-      <c r="E739" s="1"/>
+      <c r="E739" s="3"/>
     </row>
     <row r="740" ht="15" customHeight="1">
-      <c r="E740" s="1"/>
+      <c r="E740" s="3"/>
     </row>
     <row r="741" ht="15" customHeight="1">
-      <c r="E741" s="1"/>
+      <c r="E741" s="3"/>
     </row>
     <row r="742" ht="15" customHeight="1">
-      <c r="E742" s="1"/>
+      <c r="E742" s="3"/>
     </row>
     <row r="743" ht="15" customHeight="1">
-      <c r="E743" s="1"/>
+      <c r="E743" s="3"/>
     </row>
     <row r="744" ht="15" customHeight="1">
-      <c r="E744" s="1"/>
+      <c r="E744" s="3"/>
     </row>
     <row r="745" ht="15" customHeight="1">
-      <c r="E745" s="1"/>
+      <c r="E745" s="3"/>
     </row>
     <row r="746" ht="15" customHeight="1">
-      <c r="E746" s="1"/>
+      <c r="E746" s="3"/>
     </row>
     <row r="747" ht="15" customHeight="1">
-      <c r="E747" s="1"/>
+      <c r="E747" s="3"/>
     </row>
     <row r="748" ht="15" customHeight="1">
-      <c r="E748" s="1"/>
+      <c r="E748" s="3"/>
     </row>
     <row r="749" ht="15" customHeight="1">
-      <c r="E749" s="1"/>
+      <c r="E749" s="3"/>
     </row>
     <row r="750" ht="15" customHeight="1">
-      <c r="E750" s="1"/>
+      <c r="E750" s="3"/>
     </row>
     <row r="751" ht="15" customHeight="1">
-      <c r="E751" s="1"/>
+      <c r="E751" s="3"/>
     </row>
     <row r="752" ht="15" customHeight="1">
-      <c r="E752" s="1"/>
+      <c r="E752" s="3"/>
     </row>
     <row r="753" ht="15" customHeight="1">
-      <c r="E753" s="1"/>
+      <c r="E753" s="3"/>
     </row>
     <row r="754" ht="15" customHeight="1">
-      <c r="E754" s="1"/>
+      <c r="E754" s="3"/>
     </row>
     <row r="755" ht="15" customHeight="1">
-      <c r="E755" s="1"/>
+      <c r="E755" s="3"/>
     </row>
     <row r="756" ht="15" customHeight="1">
-      <c r="E756" s="1"/>
+      <c r="E756" s="3"/>
     </row>
     <row r="757" ht="15" customHeight="1">
-      <c r="E757" s="1"/>
+      <c r="E757" s="3"/>
     </row>
     <row r="758" ht="15" customHeight="1">
-      <c r="E758" s="1"/>
+      <c r="E758" s="3"/>
     </row>
     <row r="759" ht="15" customHeight="1">
-      <c r="E759" s="1"/>
+      <c r="E759" s="3"/>
     </row>
     <row r="760" ht="15" customHeight="1">
-      <c r="E760" s="1"/>
+      <c r="E760" s="3"/>
     </row>
     <row r="761" ht="15" customHeight="1">
-      <c r="E761" s="1"/>
+      <c r="E761" s="3"/>
     </row>
     <row r="762" ht="15" customHeight="1">
-      <c r="E762" s="1"/>
+      <c r="E762" s="3"/>
     </row>
     <row r="763" ht="15" customHeight="1">
-      <c r="E763" s="1"/>
+      <c r="E763" s="3"/>
     </row>
     <row r="764" ht="15" customHeight="1">
-      <c r="E764" s="1"/>
+      <c r="E764" s="3"/>
     </row>
     <row r="765" ht="15" customHeight="1">
-      <c r="E765" s="1"/>
+      <c r="E765" s="3"/>
     </row>
     <row r="766" ht="15" customHeight="1">
-      <c r="E766" s="1"/>
+      <c r="E766" s="3"/>
     </row>
     <row r="767" ht="15" customHeight="1">
-      <c r="E767" s="1"/>
+      <c r="E767" s="3"/>
     </row>
     <row r="768" ht="15" customHeight="1">
-      <c r="E768" s="1"/>
+      <c r="E768" s="3"/>
     </row>
     <row r="769" ht="15" customHeight="1">
-      <c r="E769" s="1"/>
+      <c r="E769" s="3"/>
     </row>
     <row r="770" ht="15" customHeight="1">
-      <c r="E770" s="1"/>
+      <c r="E770" s="3"/>
     </row>
     <row r="771" ht="15" customHeight="1">
-      <c r="E771" s="1"/>
+      <c r="E771" s="3"/>
     </row>
     <row r="772" ht="15" customHeight="1">
-      <c r="E772" s="1"/>
+      <c r="E772" s="3"/>
     </row>
     <row r="773" ht="15" customHeight="1">
-      <c r="E773" s="1"/>
+      <c r="E773" s="3"/>
     </row>
     <row r="774" ht="15" customHeight="1">
-      <c r="E774" s="1"/>
+      <c r="E774" s="3"/>
     </row>
     <row r="775" ht="15" customHeight="1">
-      <c r="E775" s="1"/>
+      <c r="E775" s="3"/>
     </row>
     <row r="776" ht="15" customHeight="1">
-      <c r="E776" s="1"/>
+      <c r="E776" s="3"/>
     </row>
     <row r="777" ht="15" customHeight="1">
-      <c r="E777" s="1"/>
+      <c r="E777" s="3"/>
     </row>
     <row r="778" ht="15" customHeight="1">
-      <c r="E778" s="1"/>
+      <c r="E778" s="3"/>
     </row>
     <row r="779" ht="15" customHeight="1">
-      <c r="E779" s="1"/>
+      <c r="E779" s="3"/>
     </row>
     <row r="780" ht="15" customHeight="1">
-      <c r="E780" s="1"/>
+      <c r="E780" s="3"/>
     </row>
     <row r="781" ht="15" customHeight="1">
-      <c r="E781" s="1"/>
+      <c r="E781" s="3"/>
     </row>
     <row r="782" ht="15" customHeight="1">
-      <c r="E782" s="1"/>
+      <c r="E782" s="3"/>
     </row>
     <row r="783" ht="15" customHeight="1">
-      <c r="E783" s="1"/>
+      <c r="E783" s="3"/>
     </row>
     <row r="784" ht="15" customHeight="1">
-      <c r="E784" s="1"/>
+      <c r="E784" s="3"/>
     </row>
     <row r="785" ht="15" customHeight="1">
-      <c r="E785" s="1"/>
+      <c r="E785" s="3"/>
     </row>
     <row r="786" ht="15" customHeight="1">
-      <c r="E786" s="1"/>
+      <c r="E786" s="3"/>
     </row>
     <row r="787" ht="15" customHeight="1">
-      <c r="E787" s="1"/>
+      <c r="E787" s="3"/>
     </row>
     <row r="788" ht="15" customHeight="1">
-      <c r="E788" s="1"/>
+      <c r="E788" s="3"/>
     </row>
     <row r="789" ht="15" customHeight="1">
-      <c r="E789" s="1"/>
+      <c r="E789" s="3"/>
     </row>
     <row r="790" ht="15" customHeight="1">
-      <c r="E790" s="1"/>
+      <c r="E790" s="3"/>
     </row>
     <row r="791" ht="15" customHeight="1">
-      <c r="E791" s="1"/>
+      <c r="E791" s="3"/>
     </row>
     <row r="792" ht="15" customHeight="1">
-      <c r="E792" s="1"/>
+      <c r="E792" s="3"/>
     </row>
     <row r="793" ht="15" customHeight="1">
-      <c r="E793" s="1"/>
+      <c r="E793" s="3"/>
     </row>
     <row r="794" ht="15" customHeight="1">
-      <c r="E794" s="1"/>
+      <c r="E794" s="3"/>
     </row>
     <row r="795" ht="15" customHeight="1">
-      <c r="E795" s="1"/>
+      <c r="E795" s="3"/>
     </row>
     <row r="796" ht="15" customHeight="1">
-      <c r="E796" s="1"/>
+      <c r="E796" s="3"/>
     </row>
     <row r="797" ht="15" customHeight="1">
-      <c r="E797" s="1"/>
+      <c r="E797" s="3"/>
     </row>
     <row r="798" ht="15" customHeight="1">
-      <c r="E798" s="1"/>
+      <c r="E798" s="3"/>
     </row>
     <row r="799" ht="15" customHeight="1">
-      <c r="E799" s="1"/>
+      <c r="E799" s="3"/>
     </row>
     <row r="800" ht="15" customHeight="1">
-      <c r="E800" s="1"/>
+      <c r="E800" s="3"/>
     </row>
     <row r="801" ht="15" customHeight="1">
-      <c r="E801" s="1"/>
+      <c r="E801" s="3"/>
     </row>
     <row r="802" ht="15" customHeight="1">
-      <c r="E802" s="1"/>
+      <c r="E802" s="3"/>
     </row>
     <row r="803" ht="15" customHeight="1">
-      <c r="E803" s="1"/>
+      <c r="E803" s="3"/>
     </row>
     <row r="804" ht="15" customHeight="1">
-      <c r="E804" s="1"/>
+      <c r="E804" s="3"/>
     </row>
     <row r="805" ht="15" customHeight="1">
-      <c r="E805" s="1"/>
+      <c r="E805" s="3"/>
     </row>
     <row r="806" ht="15" customHeight="1">
-      <c r="E806" s="1"/>
+      <c r="E806" s="3"/>
     </row>
     <row r="807" ht="15" customHeight="1">
-      <c r="E807" s="1"/>
+      <c r="E807" s="3"/>
     </row>
     <row r="808" ht="15" customHeight="1">
-      <c r="E808" s="1"/>
+      <c r="E808" s="3"/>
     </row>
     <row r="809" ht="15" customHeight="1">
-      <c r="E809" s="1"/>
+      <c r="E809" s="3"/>
     </row>
     <row r="810" ht="15" customHeight="1">
-      <c r="E810" s="1"/>
+      <c r="E810" s="3"/>
     </row>
     <row r="811" ht="15" customHeight="1">
-      <c r="E811" s="1"/>
+      <c r="E811" s="3"/>
     </row>
     <row r="812" ht="15" customHeight="1">
-      <c r="E812" s="1"/>
+      <c r="E812" s="3"/>
     </row>
     <row r="813" ht="15" customHeight="1">
-      <c r="E813" s="1"/>
+      <c r="E813" s="3"/>
     </row>
     <row r="814" ht="15" customHeight="1">
-      <c r="E814" s="1"/>
+      <c r="E814" s="3"/>
     </row>
     <row r="815" ht="15" customHeight="1">
-      <c r="E815" s="1"/>
+      <c r="E815" s="3"/>
     </row>
     <row r="816" ht="15" customHeight="1">
-      <c r="E816" s="1"/>
+      <c r="E816" s="3"/>
     </row>
     <row r="817" ht="15" customHeight="1">
-      <c r="E817" s="1"/>
+      <c r="E817" s="3"/>
     </row>
     <row r="818" ht="15" customHeight="1">
-      <c r="E818" s="1"/>
+      <c r="E818" s="3"/>
     </row>
     <row r="819" ht="15" customHeight="1">
-      <c r="E819" s="1"/>
+      <c r="E819" s="3"/>
     </row>
     <row r="820" ht="15" customHeight="1">
-      <c r="E820" s="1"/>
+      <c r="E820" s="3"/>
     </row>
     <row r="821" ht="15" customHeight="1">
-      <c r="E821" s="1"/>
+      <c r="E821" s="3"/>
     </row>
     <row r="822" ht="15" customHeight="1">
-      <c r="E822" s="1"/>
+      <c r="E822" s="3"/>
     </row>
     <row r="823" ht="15" customHeight="1">
-      <c r="E823" s="1"/>
+      <c r="E823" s="3"/>
     </row>
     <row r="824" ht="15" customHeight="1">
-      <c r="E824" s="1"/>
+      <c r="E824" s="3"/>
     </row>
     <row r="825" ht="15" customHeight="1">
-      <c r="E825" s="1"/>
+      <c r="E825" s="3"/>
     </row>
     <row r="826" ht="15" customHeight="1">
-      <c r="E826" s="1"/>
+      <c r="E826" s="3"/>
     </row>
     <row r="827" ht="15" customHeight="1">
-      <c r="E827" s="1"/>
+      <c r="E827" s="3"/>
     </row>
     <row r="828" ht="15" customHeight="1">
-      <c r="E828" s="1"/>
+      <c r="E828" s="3"/>
     </row>
     <row r="829" ht="15" customHeight="1">
-      <c r="E829" s="1"/>
+      <c r="E829" s="3"/>
     </row>
     <row r="830" ht="15" customHeight="1">
-      <c r="E830" s="1"/>
+      <c r="E830" s="3"/>
     </row>
     <row r="831" ht="15" customHeight="1">
-      <c r="E831" s="1"/>
+      <c r="E831" s="3"/>
     </row>
     <row r="832" ht="15" customHeight="1">
-      <c r="E832" s="1"/>
+      <c r="E832" s="3"/>
     </row>
     <row r="833" ht="15" customHeight="1">
-      <c r="E833" s="1"/>
+      <c r="E833" s="3"/>
     </row>
     <row r="834" ht="15" customHeight="1">
-      <c r="E834" s="1"/>
+      <c r="E834" s="3"/>
     </row>
     <row r="835" ht="15" customHeight="1">
-      <c r="E835" s="1"/>
+      <c r="E835" s="3"/>
     </row>
     <row r="836" ht="15" customHeight="1">
-      <c r="E836" s="1"/>
+      <c r="E836" s="3"/>
     </row>
     <row r="837" ht="15" customHeight="1">
-      <c r="E837" s="1"/>
+      <c r="E837" s="3"/>
     </row>
     <row r="838" ht="15" customHeight="1">
-      <c r="E838" s="1"/>
+      <c r="E838" s="3"/>
     </row>
     <row r="839" ht="15" customHeight="1">
-      <c r="E839" s="1"/>
+      <c r="E839" s="3"/>
     </row>
     <row r="840" ht="15" customHeight="1">
-      <c r="E840" s="1"/>
+      <c r="E840" s="3"/>
     </row>
     <row r="841" ht="15" customHeight="1">
-      <c r="E841" s="1"/>
+      <c r="E841" s="3"/>
     </row>
     <row r="842" ht="15" customHeight="1">
-      <c r="E842" s="1"/>
+      <c r="E842" s="3"/>
     </row>
     <row r="843" ht="15" customHeight="1">
-      <c r="E843" s="1"/>
+      <c r="E843" s="3"/>
     </row>
     <row r="844" ht="15" customHeight="1">
-      <c r="E844" s="1"/>
+      <c r="E844" s="3"/>
     </row>
     <row r="845" ht="15" customHeight="1">
-      <c r="E845" s="1"/>
+      <c r="E845" s="3"/>
     </row>
     <row r="846" ht="15" customHeight="1">
-      <c r="E846" s="1"/>
+      <c r="E846" s="3"/>
     </row>
     <row r="847" ht="15" customHeight="1">
-      <c r="E847" s="1"/>
+      <c r="E847" s="3"/>
     </row>
     <row r="848" ht="15" customHeight="1">
-      <c r="E848" s="1"/>
+      <c r="E848" s="3"/>
     </row>
     <row r="849" ht="15" customHeight="1">
-      <c r="E849" s="1"/>
+      <c r="E849" s="3"/>
     </row>
     <row r="850" ht="15" customHeight="1">
-      <c r="E850" s="1"/>
+      <c r="E850" s="3"/>
     </row>
     <row r="851" ht="15" customHeight="1">
-      <c r="E851" s="1"/>
+      <c r="E851" s="3"/>
     </row>
     <row r="852" ht="15" customHeight="1">
-      <c r="E852" s="1"/>
+      <c r="E852" s="3"/>
     </row>
     <row r="853" ht="15" customHeight="1">
-      <c r="E853" s="1"/>
+      <c r="E853" s="3"/>
     </row>
     <row r="854" ht="15" customHeight="1">
-      <c r="E854" s="1"/>
+      <c r="E854" s="3"/>
     </row>
     <row r="855" ht="15" customHeight="1">
-      <c r="E855" s="1"/>
+      <c r="E855" s="3"/>
     </row>
     <row r="856" ht="15" customHeight="1">
-      <c r="E856" s="1"/>
+      <c r="E856" s="3"/>
     </row>
     <row r="857" ht="15" customHeight="1">
-      <c r="E857" s="1"/>
+      <c r="E857" s="3"/>
     </row>
     <row r="858" ht="15" customHeight="1">
-      <c r="E858" s="1"/>
+      <c r="E858" s="3"/>
     </row>
     <row r="859" ht="15" customHeight="1">
-      <c r="E859" s="1"/>
+      <c r="E859" s="3"/>
     </row>
     <row r="860" ht="15" customHeight="1">
-      <c r="E860" s="1"/>
+      <c r="E860" s="3"/>
     </row>
     <row r="861" ht="15" customHeight="1">
-      <c r="E861" s="1"/>
+      <c r="E861" s="3"/>
     </row>
     <row r="862" ht="15" customHeight="1">
-      <c r="E862" s="1"/>
+      <c r="E862" s="3"/>
     </row>
     <row r="863" ht="15" customHeight="1">
-      <c r="E863" s="1"/>
+      <c r="E863" s="3"/>
     </row>
     <row r="864" ht="15" customHeight="1">
-      <c r="E864" s="1"/>
+      <c r="E864" s="3"/>
     </row>
     <row r="865" ht="15" customHeight="1">
-      <c r="E865" s="1"/>
+      <c r="E865" s="3"/>
     </row>
     <row r="866" ht="15" customHeight="1">
-      <c r="E866" s="1"/>
+      <c r="E866" s="3"/>
     </row>
     <row r="867" ht="15" customHeight="1">
-      <c r="E867" s="1"/>
+      <c r="E867" s="3"/>
     </row>
     <row r="868" ht="15" customHeight="1">
-      <c r="E868" s="1"/>
+      <c r="E868" s="3"/>
     </row>
     <row r="869" ht="15" customHeight="1">
-      <c r="E869" s="1"/>
+      <c r="E869" s="3"/>
     </row>
     <row r="870" ht="15" customHeight="1">
-      <c r="E870" s="1"/>
+      <c r="E870" s="3"/>
     </row>
     <row r="871" ht="15" customHeight="1">
-      <c r="E871" s="1"/>
+      <c r="E871" s="3"/>
     </row>
     <row r="872" ht="15" customHeight="1">
-      <c r="E872" s="1"/>
+      <c r="E872" s="3"/>
     </row>
     <row r="873" ht="15" customHeight="1">
-      <c r="E873" s="1"/>
+      <c r="E873" s="3"/>
     </row>
     <row r="874" ht="15" customHeight="1">
-      <c r="E874" s="1"/>
+      <c r="E874" s="3"/>
     </row>
     <row r="875" ht="15" customHeight="1">
-      <c r="E875" s="1"/>
+      <c r="E875" s="3"/>
     </row>
     <row r="876" ht="15" customHeight="1">
-      <c r="E876" s="1"/>
+      <c r="E876" s="3"/>
     </row>
     <row r="877" ht="15" customHeight="1">
-      <c r="E877" s="1"/>
+      <c r="E877" s="3"/>
     </row>
     <row r="878" ht="15" customHeight="1">
-      <c r="E878" s="1"/>
+      <c r="E878" s="3"/>
     </row>
     <row r="879" ht="15" customHeight="1">
-      <c r="E879" s="1"/>
+      <c r="E879" s="3"/>
     </row>
     <row r="880" ht="15" customHeight="1">
-      <c r="E880" s="1"/>
+      <c r="E880" s="3"/>
     </row>
     <row r="881" ht="15" customHeight="1">
-      <c r="E881" s="1"/>
+      <c r="E881" s="3"/>
     </row>
     <row r="882" ht="15" customHeight="1">
-      <c r="E882" s="1"/>
+      <c r="E882" s="3"/>
     </row>
     <row r="883" ht="15" customHeight="1">
-      <c r="E883" s="1"/>
+      <c r="E883" s="3"/>
     </row>
     <row r="884" ht="15" customHeight="1">
-      <c r="E884" s="1"/>
+      <c r="E884" s="3"/>
     </row>
     <row r="885" ht="15" customHeight="1">
-      <c r="E885" s="1"/>
+      <c r="E885" s="3"/>
     </row>
     <row r="886" ht="15" customHeight="1">
-      <c r="E886" s="1"/>
+      <c r="E886" s="3"/>
     </row>
     <row r="887" ht="15" customHeight="1">
-      <c r="E887" s="1"/>
+      <c r="E887" s="3"/>
     </row>
     <row r="888" ht="15" customHeight="1">
-      <c r="E888" s="1"/>
+      <c r="E888" s="3"/>
     </row>
     <row r="889" ht="15" customHeight="1">
-      <c r="E889" s="1"/>
+      <c r="E889" s="3"/>
     </row>
     <row r="890" ht="15" customHeight="1">
-      <c r="E890" s="1"/>
+      <c r="E890" s="3"/>
     </row>
     <row r="891" ht="15" customHeight="1">
-      <c r="E891" s="1"/>
+      <c r="E891" s="3"/>
     </row>
     <row r="892" ht="15" customHeight="1">
-      <c r="E892" s="1"/>
+      <c r="E892" s="3"/>
     </row>
     <row r="893" ht="15" customHeight="1">
-      <c r="E893" s="1"/>
+      <c r="E893" s="3"/>
     </row>
     <row r="894" ht="15" customHeight="1">
-      <c r="E894" s="1"/>
+      <c r="E894" s="3"/>
     </row>
     <row r="895" ht="15" customHeight="1">
-      <c r="E895" s="1"/>
+      <c r="E895" s="3"/>
     </row>
     <row r="896" ht="15" customHeight="1">
-      <c r="E896" s="1"/>
+      <c r="E896" s="3"/>
     </row>
     <row r="897" ht="15" customHeight="1">
-      <c r="E897" s="1"/>
+      <c r="E897" s="3"/>
     </row>
     <row r="898" ht="15" customHeight="1">
-      <c r="E898" s="1"/>
+      <c r="E898" s="3"/>
     </row>
     <row r="899" ht="15" customHeight="1">
-      <c r="E899" s="1"/>
+      <c r="E899" s="3"/>
     </row>
     <row r="900" ht="15" customHeight="1">
-      <c r="E900" s="1"/>
+      <c r="E900" s="3"/>
     </row>
     <row r="901" ht="15" customHeight="1">
-      <c r="E901" s="1"/>
+      <c r="E901" s="3"/>
     </row>
     <row r="902" ht="15" customHeight="1">
-      <c r="E902" s="1"/>
+      <c r="E902" s="3"/>
     </row>
     <row r="903" ht="15" customHeight="1">
-      <c r="E903" s="1"/>
+      <c r="E903" s="3"/>
     </row>
     <row r="904" ht="15" customHeight="1">
-      <c r="E904" s="1"/>
+      <c r="E904" s="3"/>
     </row>
     <row r="905" ht="15" customHeight="1">
-      <c r="E905" s="1"/>
+      <c r="E905" s="3"/>
     </row>
     <row r="906" ht="15" customHeight="1">
-      <c r="E906" s="1"/>
+      <c r="E906" s="3"/>
     </row>
     <row r="907" ht="15" customHeight="1">
-      <c r="E907" s="1"/>
+      <c r="E907" s="3"/>
     </row>
     <row r="908" ht="15" customHeight="1">
-      <c r="E908" s="1"/>
+      <c r="E908" s="3"/>
     </row>
     <row r="909" ht="15" customHeight="1">
-      <c r="E909" s="1"/>
+      <c r="E909" s="3"/>
     </row>
     <row r="910" ht="15" customHeight="1">
-      <c r="E910" s="1"/>
+      <c r="E910" s="3"/>
     </row>
     <row r="911" ht="15" customHeight="1">
-      <c r="E911" s="1"/>
+      <c r="E911" s="3"/>
     </row>
     <row r="912" ht="15" customHeight="1">
-      <c r="E912" s="1"/>
+      <c r="E912" s="3"/>
     </row>
     <row r="913" ht="15" customHeight="1">
-      <c r="E913" s="1"/>
+      <c r="E913" s="3"/>
     </row>
     <row r="914" ht="15" customHeight="1">
-      <c r="E914" s="1"/>
+      <c r="E914" s="3"/>
     </row>
     <row r="915" ht="15" customHeight="1">
-      <c r="E915" s="1"/>
+      <c r="E915" s="3"/>
     </row>
     <row r="916" ht="15" customHeight="1">
-      <c r="E916" s="1"/>
+      <c r="E916" s="3"/>
     </row>
     <row r="917" ht="15" customHeight="1">
-      <c r="E917" s="1"/>
+      <c r="E917" s="3"/>
     </row>
     <row r="918" ht="15" customHeight="1">
-      <c r="E918" s="1"/>
+      <c r="E918" s="3"/>
     </row>
     <row r="919" ht="15" customHeight="1">
-      <c r="E919" s="1"/>
+      <c r="E919" s="3"/>
     </row>
     <row r="920" ht="15" customHeight="1">
-      <c r="E920" s="1"/>
+      <c r="E920" s="3"/>
     </row>
     <row r="921" ht="15" customHeight="1">
-      <c r="E921" s="1"/>
+      <c r="E921" s="3"/>
     </row>
     <row r="922" ht="15" customHeight="1">
-      <c r="E922" s="1"/>
+      <c r="E922" s="3"/>
     </row>
     <row r="923" ht="15" customHeight="1">
-      <c r="E923" s="1"/>
+      <c r="E923" s="3"/>
     </row>
     <row r="924" ht="15" customHeight="1">
-      <c r="E924" s="1"/>
+      <c r="E924" s="3"/>
     </row>
     <row r="925" ht="15" customHeight="1">
-      <c r="E925" s="1"/>
+      <c r="E925" s="3"/>
     </row>
     <row r="926" ht="15" customHeight="1">
-      <c r="E926" s="1"/>
+      <c r="E926" s="3"/>
     </row>
     <row r="927" ht="15" customHeight="1">
-      <c r="E927" s="1"/>
+      <c r="E927" s="3"/>
     </row>
     <row r="928" ht="15" customHeight="1">
-      <c r="E928" s="1"/>
+      <c r="E928" s="3"/>
     </row>
     <row r="929" ht="15" customHeight="1">
-      <c r="E929" s="1"/>
+      <c r="E929" s="3"/>
     </row>
     <row r="930" ht="15" customHeight="1">
-      <c r="E930" s="1"/>
+      <c r="E930" s="3"/>
     </row>
     <row r="931" ht="15" customHeight="1">
-      <c r="E931" s="1"/>
+      <c r="E931" s="3"/>
     </row>
     <row r="932" ht="15" customHeight="1">
-      <c r="E932" s="1"/>
+      <c r="E932" s="3"/>
     </row>
     <row r="933" ht="15" customHeight="1">
-      <c r="E933" s="1"/>
+      <c r="E933" s="3"/>
     </row>
     <row r="934" ht="15" customHeight="1">
-      <c r="E934" s="1"/>
+      <c r="E934" s="3"/>
     </row>
     <row r="935" ht="15" customHeight="1">
-      <c r="E935" s="1"/>
+      <c r="E935" s="3"/>
     </row>
     <row r="936" ht="15" customHeight="1">
-      <c r="E936" s="1"/>
+      <c r="E936" s="3"/>
     </row>
     <row r="937" ht="15" customHeight="1">
-      <c r="E937" s="1"/>
+      <c r="E937" s="3"/>
     </row>
     <row r="938" ht="15" customHeight="1">
-      <c r="E938" s="1"/>
+      <c r="E938" s="3"/>
     </row>
     <row r="939" ht="15" customHeight="1">
-      <c r="E939" s="1"/>
+      <c r="E939" s="3"/>
     </row>
     <row r="940" ht="15" customHeight="1">
-      <c r="E940" s="1"/>
+      <c r="E940" s="3"/>
     </row>
     <row r="941" ht="15" customHeight="1">
-      <c r="E941" s="1"/>
+      <c r="E941" s="3"/>
     </row>
     <row r="942" ht="15" customHeight="1">
-      <c r="E942" s="1"/>
+      <c r="E942" s="3"/>
     </row>
     <row r="943" ht="15" customHeight="1">
-      <c r="E943" s="1"/>
+      <c r="E943" s="3"/>
     </row>
     <row r="944" ht="15" customHeight="1">
-      <c r="E944" s="1"/>
+      <c r="E944" s="3"/>
     </row>
     <row r="945" ht="15" customHeight="1">
-      <c r="E945" s="1"/>
+      <c r="E945" s="3"/>
     </row>
     <row r="946" ht="15" customHeight="1">
-      <c r="E946" s="1"/>
+      <c r="E946" s="3"/>
     </row>
     <row r="947" ht="15" customHeight="1">
-      <c r="E947" s="1"/>
+      <c r="E947" s="3"/>
     </row>
     <row r="948" ht="15" customHeight="1">
-      <c r="E948" s="1"/>
+      <c r="E948" s="3"/>
     </row>
     <row r="949" ht="15" customHeight="1">
-      <c r="E949" s="1"/>
+      <c r="E949" s="3"/>
     </row>
     <row r="950" ht="15" customHeight="1">
-      <c r="E950" s="1"/>
+      <c r="E950" s="3"/>
     </row>
     <row r="951" ht="15" customHeight="1">
-      <c r="E951" s="1"/>
+      <c r="E951" s="3"/>
     </row>
     <row r="952" ht="15" customHeight="1">
-      <c r="E952" s="1"/>
+      <c r="E952" s="3"/>
     </row>
     <row r="953" ht="15" customHeight="1">
-      <c r="E953" s="1"/>
+      <c r="E953" s="3"/>
     </row>
     <row r="954" ht="15" customHeight="1">
-      <c r="E954" s="1"/>
+      <c r="E954" s="3"/>
     </row>
     <row r="955" ht="15" customHeight="1">
-      <c r="E955" s="1"/>
+      <c r="E955" s="3"/>
     </row>
     <row r="956" ht="15" customHeight="1">
-      <c r="E956" s="1"/>
+      <c r="E956" s="3"/>
     </row>
     <row r="957" ht="15" customHeight="1">
-      <c r="E957" s="1"/>
+      <c r="E957" s="3"/>
     </row>
     <row r="958" ht="15" customHeight="1">
-      <c r="E958" s="1"/>
+      <c r="E958" s="3"/>
     </row>
     <row r="959" ht="15" customHeight="1">
-      <c r="E959" s="1"/>
+      <c r="E959" s="3"/>
     </row>
     <row r="960" ht="15" customHeight="1">
-      <c r="E960" s="1"/>
+      <c r="E960" s="3"/>
     </row>
     <row r="961" ht="15" customHeight="1">
-      <c r="E961" s="1"/>
+      <c r="E961" s="3"/>
     </row>
     <row r="962" ht="15" customHeight="1">
-      <c r="E962" s="1"/>
+      <c r="E962" s="3"/>
     </row>
     <row r="963" ht="15" customHeight="1">
-      <c r="E963" s="1"/>
+      <c r="E963" s="3"/>
     </row>
     <row r="964" ht="15" customHeight="1">
-      <c r="E964" s="1"/>
+      <c r="E964" s="3"/>
     </row>
     <row r="965" ht="15" customHeight="1">
-      <c r="E965" s="1"/>
+      <c r="E965" s="3"/>
     </row>
     <row r="966" ht="15" customHeight="1">
-      <c r="E966" s="1"/>
+      <c r="E966" s="3"/>
     </row>
     <row r="967" ht="15" customHeight="1">
-      <c r="E967" s="1"/>
+      <c r="E967" s="3"/>
     </row>
     <row r="968" ht="15" customHeight="1">
-      <c r="E968" s="1"/>
+      <c r="E968" s="3"/>
     </row>
     <row r="969" ht="15" customHeight="1">
-      <c r="E969" s="1"/>
+      <c r="E969" s="3"/>
     </row>
     <row r="970" ht="15" customHeight="1">
-      <c r="E970" s="1"/>
+      <c r="E970" s="3"/>
     </row>
     <row r="971" ht="15" customHeight="1">
-      <c r="E971" s="1"/>
+      <c r="E971" s="3"/>
     </row>
     <row r="972" ht="15" customHeight="1">
-      <c r="E972" s="1"/>
+      <c r="E972" s="3"/>
     </row>
     <row r="973" ht="15" customHeight="1">
-      <c r="E973" s="1"/>
+      <c r="E973" s="3"/>
     </row>
     <row r="974" ht="15" customHeight="1">
-      <c r="E974" s="1"/>
+      <c r="E974" s="3"/>
     </row>
     <row r="975" ht="15" customHeight="1">
-      <c r="E975" s="1"/>
+      <c r="E975" s="3"/>
     </row>
     <row r="976" ht="15" customHeight="1">
-      <c r="E976" s="1"/>
+      <c r="E976" s="3"/>
     </row>
     <row r="977" ht="15" customHeight="1">
-      <c r="E977" s="1"/>
+      <c r="E977" s="3"/>
     </row>
     <row r="978" ht="15" customHeight="1">
-      <c r="E978" s="1"/>
+      <c r="E978" s="3"/>
     </row>
     <row r="979" ht="15" customHeight="1">
-      <c r="E979" s="1"/>
+      <c r="E979" s="3"/>
     </row>
     <row r="980" ht="15" customHeight="1">
-      <c r="E980" s="1"/>
+      <c r="E980" s="3"/>
     </row>
     <row r="981" ht="15" customHeight="1">
-      <c r="E981" s="1"/>
+      <c r="E981" s="3"/>
     </row>
     <row r="982" ht="15" customHeight="1">
-      <c r="E982" s="1"/>
+      <c r="E982" s="3"/>
     </row>
     <row r="983" ht="15" customHeight="1">
-      <c r="E983" s="1"/>
+      <c r="E983" s="3"/>
     </row>
     <row r="984" ht="15" customHeight="1">
-      <c r="E984" s="1"/>
+      <c r="E984" s="3"/>
     </row>
     <row r="985" ht="15" customHeight="1">
-      <c r="E985" s="1"/>
+      <c r="E985" s="3"/>
     </row>
     <row r="986" ht="15" customHeight="1">
-      <c r="E986" s="1"/>
+      <c r="E986" s="3"/>
     </row>
     <row r="987" ht="15" customHeight="1">
-      <c r="E987" s="1"/>
+      <c r="E987" s="3"/>
     </row>
     <row r="988" ht="15" customHeight="1">
-      <c r="E988" s="1"/>
+      <c r="E988" s="3"/>
     </row>
     <row r="989" ht="15" customHeight="1">
-      <c r="E989" s="1"/>
+      <c r="E989" s="3"/>
     </row>
     <row r="990" ht="15" customHeight="1">
-      <c r="E990" s="1"/>
+      <c r="E990" s="3"/>
     </row>
     <row r="991" ht="15" customHeight="1">
-      <c r="E991" s="1"/>
+      <c r="E991" s="3"/>
     </row>
     <row r="992" ht="15" customHeight="1">
-      <c r="E992" s="1"/>
+      <c r="E992" s="3"/>
     </row>
     <row r="993" ht="15" customHeight="1">
-      <c r="E993" s="1"/>
+      <c r="E993" s="3"/>
     </row>
     <row r="994" ht="15" customHeight="1">
-      <c r="E994" s="1"/>
+      <c r="E994" s="3"/>
     </row>
     <row r="995" ht="15" customHeight="1">
-      <c r="E995" s="1"/>
+      <c r="E995" s="3"/>
     </row>
     <row r="996" ht="15" customHeight="1">
-      <c r="E996" s="1"/>
+      <c r="E996" s="3"/>
     </row>
     <row r="997" ht="15" customHeight="1">
-      <c r="E997" s="1"/>
+      <c r="E997" s="3"/>
     </row>
     <row r="998" ht="15" customHeight="1">
-      <c r="E998" s="1"/>
+      <c r="E998" s="3"/>
     </row>
     <row r="999" ht="15" customHeight="1">
-      <c r="E999" s="1"/>
+      <c r="E999" s="3"/>
     </row>
     <row r="1000" ht="15" customHeight="1">
-      <c r="E1000" s="1"/>
+      <c r="E1000" s="3"/>
     </row>
     <row r="1001" ht="15" customHeight="1">
-      <c r="E1001" s="1"/>
+      <c r="E1001" s="3"/>
     </row>
     <row r="1002" ht="15" customHeight="1">
-      <c r="E1002" s="1"/>
+      <c r="E1002" s="3"/>
     </row>
     <row r="1003" ht="15" customHeight="1">
-      <c r="E1003" s="1"/>
+      <c r="E1003" s="3"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="E3:E1003" type="list">
-      <formula1>"tp Individual,tp Aggregated,pk Individual,pk Aggregated"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.7" right="0.7" top="0.634722222222222" bottom="0.634722222222222" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
     <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
     <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DataFiles_DataClass_5</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DataFiles_DataClass_5</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DataFiles_DataClass_5</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DataFiles_DataClass_5</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DataFiles_DataClass_5</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DataFiles_DataClass_5</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DataFiles_DataClass_5</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DataFiles_DataClass_5</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -3926,514 +3979,495 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" ht="35.05" customHeight="1">
-      <c r="A2" s="3" t="s">
+    <row r="2" ht="34.5" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="G2" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="C3" s="3" t="s">
         <v>30</v>
       </c>
+      <c r="G3" s="6" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="C4" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="G4" s="6" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="B5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>37</v>
       </c>
+      <c r="G5" s="6" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="A6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="B6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="F6" s="3" t="s">
         <v>41</v>
       </c>
+      <c r="G6" s="6" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="B7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="G7" s="6" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="A8" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="B8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>47</v>
       </c>
+      <c r="G8" s="6" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="A9" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="B9" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="C9" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="D9" s="3" t="s">
         <v>52</v>
       </c>
+      <c r="G9" s="6" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="A10" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="B10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>55</v>
       </c>
+      <c r="G10" s="6" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="B11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>58</v>
       </c>
+      <c r="G11" s="6" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="A12" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="B12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>61</v>
       </c>
+      <c r="G12" s="6" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="13" ht="31.5" customHeight="1">
-      <c r="A13" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="1" t="s">
+      <c r="A13" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="B13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="14" ht="23.85" customHeight="1">
-      <c r="A14" s="1" t="s">
+      <c r="G13" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="1" t="s">
+    </row>
+    <row r="14" ht="23.25" customHeight="1">
+      <c r="A14" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="B14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="15" ht="23.85" customHeight="1">
-      <c r="A15" s="1" t="s">
+      <c r="G14" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="1" t="s">
+    </row>
+    <row r="15" ht="23.25" customHeight="1">
+      <c r="A15" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="B15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="16" ht="23.85" customHeight="1">
-      <c r="A16" s="1" t="s">
+    <row r="16" ht="23.25" customHeight="1">
+      <c r="A16" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16" s="8" t="s">
+      <c r="B16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="6" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G17" s="8" t="s">
+      <c r="B17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="6" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="1" t="s">
+      <c r="B18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="6" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="6" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="6" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="6" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22" ht="23.85" customHeight="1">
-      <c r="A22" s="1" t="s">
+    <row r="22" ht="23.25" customHeight="1">
+      <c r="A22" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" s="6" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="23" ht="23.85" customHeight="1">
-      <c r="A23" s="4" t="s">
+    <row r="23" ht="23.25" customHeight="1">
+      <c r="A23" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" s="6" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="24" ht="23.85" customHeight="1">
-      <c r="A24" s="4" t="s">
+    <row r="24" ht="23.25" customHeight="1">
+      <c r="A24" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E25" s="1" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="F25" s="1" t="s">
+      <c r="E25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="6" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="27" ht="23.85" customHeight="1">
-      <c r="A27" s="4" t="s">
+    <row r="27" ht="23.25" customHeight="1">
+      <c r="A27" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G27" s="8" t="s">
+      <c r="B27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="28" ht="23.85" customHeight="1">
-      <c r="A28" s="1" t="s">
+    <row r="28" ht="23.25" customHeight="1">
+      <c r="A28" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G28" s="8" t="s">
+      <c r="B28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="29" ht="23.85" customHeight="1">
-      <c r="A29" s="1" t="s">
+    <row r="29" ht="23.25" customHeight="1">
+      <c r="A29" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G29" s="8" t="s">
+      <c r="B29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="30" ht="23.85" customHeight="1">
-      <c r="A30" s="4" t="s">
+    <row r="30" ht="23.25" customHeight="1">
+      <c r="A30" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G30" s="8" t="s">
+      <c r="B30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="31" ht="23.85" customHeight="1">
-      <c r="A31" s="4" t="s">
+    <row r="31" ht="23.25" customHeight="1">
+      <c r="A31" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G31" s="8" t="s">
+      <c r="B31" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="6" t="s">
         <v>103</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3:B1031" type="list">
-      <formula1>"identifier,timeprofile,biometrics,covariate,metadata"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
+  <dataValidations count="3">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="F13" type="list">
       <formula1>"ArithmeticStdDev,GeometricStdDev"</formula1>
       <formula2>0</formula2>
@@ -4447,12 +4481,94 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.7" right="0.7" top="0.634722222222222" bottom="0.634722222222222" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
     <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
     <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_tpDictionary_Type_7</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_tpDictionary_Type_7</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_tpDictionary_Type_7</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_tpDictionary_Type_7</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_tpDictionary_Type_7</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_tpDictionary_Type_7</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_tpDictionary_Type_7</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_tpDictionary_Type_7</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -4472,486 +4588,463 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" ht="35.05" customHeight="1">
-      <c r="A2" s="3" t="s">
+    <row r="2" ht="34.5" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>26</v>
+      <c r="F2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="C3" s="3" t="s">
         <v>30</v>
       </c>
+      <c r="G3" s="6" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="C4" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="G4" s="6" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="B5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>37</v>
       </c>
+      <c r="G5" s="6" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="A6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="B6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="F6" s="3" t="s">
         <v>41</v>
       </c>
+      <c r="G6" s="6" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>44</v>
+      <c r="B7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="A8" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="B8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>47</v>
       </c>
+      <c r="G8" s="6" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>109</v>
+      <c r="A9" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" s="8" t="s">
+      <c r="A10" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>55</v>
       </c>
+      <c r="G10" s="6" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11" s="8" t="s">
+      <c r="C11" s="3" t="s">
         <v>58</v>
       </c>
+      <c r="G11" s="6" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="12" ht="31.5" customHeight="1">
-      <c r="A12" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" ht="23.85" customHeight="1">
-      <c r="A13" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13" s="8" t="s">
+      <c r="A12" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" ht="23.25" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="14" ht="23.85" customHeight="1">
-      <c r="A14" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G14" s="8" t="s">
+      <c r="G13" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" ht="23.25" customHeight="1">
+      <c r="A14" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="15" ht="23.85" customHeight="1">
-      <c r="A15" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G15" s="8" t="s">
+    <row r="15" ht="23.25" customHeight="1">
+      <c r="A15" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="6" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>117</v>
+      <c r="B16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="6" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G17" s="8" t="s">
-        <v>118</v>
+      <c r="G17" s="6" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G18" s="8" t="s">
-        <v>119</v>
+      <c r="G18" s="6" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G19" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" ht="23.85" customHeight="1">
-      <c r="A20" s="1" t="s">
+      <c r="G19" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" ht="23.25" customHeight="1">
+      <c r="A20" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="6" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="21" ht="23.85" customHeight="1">
-      <c r="A21" s="4" t="s">
+    <row r="21" ht="23.25" customHeight="1">
+      <c r="A21" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="6" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="22" ht="23.85" customHeight="1">
-      <c r="A22" s="4" t="s">
+    <row r="22" ht="23.25" customHeight="1">
+      <c r="A22" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="1" t="b">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="F23" s="1" t="s">
+      <c r="E23" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" s="6" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="25" ht="23.85" customHeight="1">
-      <c r="A25" s="4" t="s">
+    <row r="25" ht="23.25" customHeight="1">
+      <c r="A25" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G25" s="8" t="s">
+      <c r="B25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="26" ht="23.85" customHeight="1">
-      <c r="A26" s="1" t="s">
+    <row r="26" ht="23.25" customHeight="1">
+      <c r="A26" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G26" s="8" t="s">
+      <c r="B26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="27" ht="23.85" customHeight="1">
-      <c r="A27" s="1" t="s">
+    <row r="27" ht="23.25" customHeight="1">
+      <c r="A27" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G27" s="8" t="s">
+      <c r="B27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="28" ht="23.85" customHeight="1">
-      <c r="A28" s="4" t="s">
+    <row r="28" ht="23.25" customHeight="1">
+      <c r="A28" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G28" s="8" t="s">
+      <c r="B28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="29" ht="23.85" customHeight="1">
-      <c r="A29" s="4" t="s">
+    <row r="29" ht="23.25" customHeight="1">
+      <c r="A29" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G29" s="8" t="s">
+      <c r="B29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="6" t="s">
         <v>103</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3:B8 B17:B1029" type="list">
-      <formula1>"identifier,timeprofile,biometrics,covariate,metadata"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
+  <dataValidations count="3">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="F21:F22" type="list">
       <formula1>"Asian_Tanaka_1996,BlackAmerican_NHANES_1997,European_ICRP_2002,Japanese_Population,MexicanAmericanWhite_NHANES_1997,Pregnant,Preterm,WhiteAmerican_NHANES_1997"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="A9:B9 B10:B16" type="list">
-      <formula1>"identifier,pkParameter,biometrics,covariate,metadata"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="F23" type="list">
@@ -4963,8 +5056,181 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.7" right="0.7" top="0.634722222222222" bottom="0.634722222222222" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
+  </headerFooter>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_pkDictionary_Type_14</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_pkDictionary_Type_14</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_pkDictionary_Type_14</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_pkDictionary_Type_14</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_pkDictionary_Type_14</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_pkDictionary_Type_14</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_pkDictionary_Type_14</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_pkDictionary_Type_14</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="21.56" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="3" max="3" width="16.97" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="5" max="5" width="30.09" hidden="false" outlineLevel="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" ht="23.85" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
     <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
     <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
@@ -4972,77 +5238,92 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="45.71" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E1" t="s">
-        <v>21</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E2" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E3" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B4" t="s">
-        <v>135</v>
-      </c>
-      <c r="C4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E4" t="s">
-        <v>137</v>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/inst/templates/DataImportConfiguration.xlsx
+++ b/inst/templates/DataImportConfiguration.xlsx
@@ -14,16 +14,15 @@
     <sheet name="_Validity" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="validity_DataFiles_DataClass_5">'_Validity'!$A$2:$A$6</definedName>
-    <definedName name="validity_tpDictionary_Type_7">'_Validity'!$A$8:$A$12</definedName>
-    <definedName name="validity_pkDictionary_Type_14">'_Validity'!$A$14:$A$18</definedName>
+    <definedName name="validity_dataclassValues">'_Validity'!$A$1:$A$5</definedName>
+    <definedName name="validity_dictionaryTypeValues">'_Validity'!$A$7:$A$11</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="152">
   <si>
     <t xml:space="preserve">FileIdentifier</t>
   </si>
@@ -467,6 +466,18 @@
   </si>
   <si>
     <t xml:space="preserve">numericValues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tp Aggregated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pk Individual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pk Aggregated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">numeric Values</t>
   </si>
 </sst>
 </file>
@@ -3959,6 +3970,56 @@
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DataFiles_DataClass_5</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DataFiles_DataClass_5</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DataFiles_DataClass_5</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DataFiles_DataClass_5</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_dataclassValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
   </extLst>
 </worksheet>
 </file>
@@ -4568,6 +4629,56 @@
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_tpDictionary_Type_7</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_tpDictionary_Type_7</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_tpDictionary_Type_7</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_tpDictionary_Type_7</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_dictionaryTypeValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
   </extLst>
 </worksheet>
 </file>
@@ -5143,6 +5254,56 @@
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_pkDictionary_Type_14</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_pkDictionary_Type_14</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_pkDictionary_Type_14</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_pkDictionary_Type_14</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_dictionaryTypeValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
   </extLst>
 </worksheet>
 </file>
@@ -5248,81 +5409,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>142</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>147</v>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
         <v>33</v>
       </c>
     </row>

--- a/inst/templates/DataImportConfiguration.xlsx
+++ b/inst/templates/DataImportConfiguration.xlsx
@@ -3894,126 +3894,6 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>validity_DataFiles_DataClass_5</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DataFiles_DataClass_5</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DataFiles_DataClass_5</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DataFiles_DataClass_5</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DataFiles_DataClass_5</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DataFiles_DataClass_5</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DataFiles_DataClass_5</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DataFiles_DataClass_5</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DataFiles_DataClass_5</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DataFiles_DataClass_5</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DataFiles_DataClass_5</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DataFiles_DataClass_5</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
             <xm:f>validity_dataclassValues</xm:f>
           </x14:formula1>
           <xm:sqref>E2:E1048576</xm:sqref>
@@ -4549,126 +4429,6 @@
     <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_tpDictionary_Type_7</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_tpDictionary_Type_7</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_tpDictionary_Type_7</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_tpDictionary_Type_7</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_tpDictionary_Type_7</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_tpDictionary_Type_7</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_tpDictionary_Type_7</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_tpDictionary_Type_7</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_tpDictionary_Type_7</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_tpDictionary_Type_7</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_tpDictionary_Type_7</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_tpDictionary_Type_7</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
@@ -5178,126 +4938,6 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>validity_pkDictionary_Type_14</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_pkDictionary_Type_14</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_pkDictionary_Type_14</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_pkDictionary_Type_14</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_pkDictionary_Type_14</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_pkDictionary_Type_14</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_pkDictionary_Type_14</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_pkDictionary_Type_14</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_pkDictionary_Type_14</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_pkDictionary_Type_14</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_pkDictionary_Type_14</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_pkDictionary_Type_14</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
             <xm:f>validity_dictionaryTypeValues</xm:f>
           </x14:formula1>
           <xm:sqref>B2:B1048576</xm:sqref>
